--- a/イベント統計データ.xlsx
+++ b/イベント統計データ.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ca\卒研\Event Day\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6917B2A2-00DC-45CC-BD4F-7B6BE2639F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B166E9D3-9791-4B8C-AF80-EE25DE82B514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A6CF68C4-3B23-44CC-A8D2-418C0C662BC4}"/>
+    <workbookView xWindow="3350" yWindow="1070" windowWidth="16200" windowHeight="10080" xr2:uid="{A6CF68C4-3B23-44CC-A8D2-418C0C662BC4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="55">
   <si>
     <t>2024年～2026年台湾プロ野球各球団のイベントデー集計</t>
     <rPh sb="4" eb="5">
@@ -92,13 +92,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>試合</t>
-    <rPh sb="0" eb="2">
-      <t>シアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>球団名</t>
     <rPh sb="0" eb="2">
       <t>キュウダン</t>
@@ -107,24 +100,6 @@
       <t>メイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>統一獅 </t>
-  </si>
-  <si>
-    <t>中信兄弟 </t>
-  </si>
-  <si>
-    <t>樂天桃猿 </t>
-  </si>
-  <si>
-    <t>台鋼雄鷹 </t>
-  </si>
-  <si>
-    <t>富邦 </t>
-  </si>
-  <si>
-    <t>味全龍</t>
   </si>
   <si>
     <t>中信ブラザーズ</t>
@@ -256,15 +231,317 @@
     <t>台東第一棒球場</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>進化EVOLUTION！中信兄弟主場開幕戰！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SHAKE IT 碰碰狐鯊魚寶寶的快樂小夥伴</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コラボ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>蠟筆小新</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>大巨蛋防衛隊！參上！</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーズン</t>
+  </si>
+  <si>
+    <t>前半戦</t>
+    <rPh sb="0" eb="3">
+      <t>ゼンハンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後半戦</t>
+    <rPh sb="0" eb="3">
+      <t>コウハンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中信ブラザーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>楽天モンキーズ</t>
+    <rPh sb="0" eb="2">
+      <t>ラクテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TSGホークス</t>
+  </si>
+  <si>
+    <t>TSGホークス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>富邦ガーディアンズ</t>
+  </si>
+  <si>
+    <t>富邦ガーディアンズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味全ドラゴンズ</t>
+  </si>
+  <si>
+    <t>味全ドラゴンズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>ROOM835</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> 睡衣PARTY</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>品客FUN-開罐POP！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>GAME START</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>小象的異想世界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> EDDY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>'S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> WONDERLAND</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>洲際高校野球部：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>直球對決吧！學長！</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暑假限定！國語作業簿 涼水祭</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ChannelB Vol.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>K歌主題週</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対戦相手</t>
+    <rPh sb="0" eb="2">
+      <t>タイセン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>アイテ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統一7-11ライオンズ</t>
+  </si>
+  <si>
+    <t>統一7-11ライオンズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>華麗對決，咖哩必勝！今夜は華麗に勝つ！</t>
+    <rPh sb="10" eb="12">
+      <t>コンヤ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カレイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飛べ最強的王者</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サイキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>オウジャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>熱血動漫IP聯名 排球少年</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新風X進化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>讀賣巨人X中信兄弟</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動物冰友會</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>超萌IP聯寵物日 Pingu</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="185" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,6 +561,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
@@ -310,23 +601,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="185" formatCode="yyyy/mm/dd"/>
+      <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -342,18 +639,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}" name="EventSummary" displayName="EventSummary" ref="A2:G30" totalsRowShown="0">
-  <autoFilter ref="A2:G30" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}" name="EventSummary" displayName="EventSummary" ref="A2:I58" totalsRowShown="0">
+  <autoFilter ref="A2:I58" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{E394152D-5251-42F2-BBA6-4EC4F2D9A954}" name="球団"/>
-    <tableColumn id="2" xr3:uid="{34B3AD93-C8CB-42CC-91C6-D60735EAC90E}" name="年月日" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{17EC21EA-E31F-4527-98DD-D196942E795D}" name="試合"/>
+    <tableColumn id="2" xr3:uid="{34B3AD93-C8CB-42CC-91C6-D60735EAC90E}" name="年月日" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{860E6FF3-7022-4C6F-B9B7-6B4EB6509D1B}" name="シーズン" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{17EC21EA-E31F-4527-98DD-D196942E795D}" name="対戦相手"/>
     <tableColumn id="7" xr3:uid="{F6D5D400-D300-4F98-8BB2-591905FE1FFC}" name="スタジアム"/>
     <tableColumn id="4" xr3:uid="{FB090584-30CC-4B9B-8EB4-81189F638591}" name="イベント名"/>
     <tableColumn id="5" xr3:uid="{957FB07F-2C77-4F75-8606-3AF51C9B0BDA}" name="イベント内容"/>
+    <tableColumn id="8" xr3:uid="{5F75036D-5C75-449E-BE7B-25647D498D63}" name="コラボ"/>
     <tableColumn id="6" xr3:uid="{3A04F637-BFC5-4720-880B-D415C01BEBF9}" name="ゲスト"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9251663-B3A5-4A47-897B-3F44A7592C67}" name="TeamName" displayName="TeamName" ref="L2:L8" totalsRowShown="0">
+  <autoFilter ref="L2:L8" xr:uid="{A9251663-B3A5-4A47-897B-3F44A7592C67}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{886E8D62-BC01-448C-BA3E-337CB9FDC252}" name="球団名"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -654,22 +963,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FFA7CF5-486E-4A81-908D-5B6B06AA399E}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="11.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -677,440 +990,1210 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1">
         <v>45385</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1">
         <v>45386</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
         <v>45395</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1">
         <v>45396</v>
       </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>45409</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>45410</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1">
         <v>45416</v>
       </c>
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1">
         <v>45417</v>
       </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1">
         <v>45430</v>
       </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B12" s="1">
         <v>45431</v>
       </c>
+      <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B13" s="1">
         <v>45451</v>
       </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B14" s="1">
         <v>45452</v>
       </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B15" s="1">
         <v>45458</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>29</v>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B16" s="1">
         <v>45459</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>29</v>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B17" s="1">
         <v>45486</v>
       </c>
+      <c r="C17" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B18" s="1">
         <v>45487</v>
       </c>
+      <c r="C18" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B19" s="1">
         <v>45507</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>29</v>
+      <c r="C19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B20" s="1">
         <v>45508</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>29</v>
+      <c r="C20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>35</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F20" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B21" s="1">
         <v>45517</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>30</v>
+      <c r="C21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B22" s="1">
         <v>45518</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>30</v>
+      <c r="C22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F22" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B23" s="1">
         <v>45521</v>
       </c>
+      <c r="C23" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>33</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B24" s="1">
         <v>45522</v>
       </c>
+      <c r="C24" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>33</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B25" s="1">
         <v>45528</v>
       </c>
+      <c r="C25" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B26" s="1">
         <v>45529</v>
       </c>
+      <c r="C26" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D26" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B27" s="1">
         <v>45542</v>
       </c>
+      <c r="C27" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+      <c r="F27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B28" s="1">
         <v>45543</v>
       </c>
+      <c r="C28" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+      <c r="F28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B29" s="1">
         <v>45556</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B30" s="1">
         <v>45557</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="C30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="1">
+        <v>45745</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="1">
+        <v>45746</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="1">
+        <v>45751</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="1">
+        <v>45752</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="1">
+        <v>45753</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="1">
+        <v>45766</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="1">
+        <v>45767</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="1">
+        <v>45787</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="1">
+        <v>45788</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" t="s">
+        <v>33</v>
+      </c>
+      <c r="E39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="1">
+        <v>45794</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="1">
+        <v>45795</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="1">
+        <v>45807</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="1">
+        <v>45808</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="1">
+        <v>45809</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E44" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="1">
+        <v>45829</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="1">
+        <v>45830</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="1">
+        <v>45850</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="1">
+        <v>45851</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" t="s">
+        <v>37</v>
+      </c>
+      <c r="E48" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="1">
+        <v>45871</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="1">
+        <v>45872</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F50" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="1">
+        <v>45878</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="1">
+        <v>45879</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="1">
+        <v>45892</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" t="s">
+        <v>33</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="1">
+        <v>45893</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" t="s">
+        <v>33</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="1">
+        <v>45906</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E55" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46272</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" t="s">
+        <v>46</v>
+      </c>
+      <c r="E56" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="1">
+        <v>45920</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D57" t="s">
+        <v>37</v>
+      </c>
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="1">
+        <v>45921</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" t="s">
+        <v>37</v>
+      </c>
+      <c r="E58" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A58" xr:uid="{AE6A38C0-572D-4047-B9F9-1FC7841EE013}">
+      <formula1>$L$2:$L$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C58" xr:uid="{4EFB52BD-777A-49C0-AB2C-CA7A84FB8040}">
+      <formula1>$M$3:$M$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{E06B60E4-D0A3-4733-BC22-8A777CB2F035}">
+      <formula1>$L$3:$L$8</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/イベント統計データ.xlsx
+++ b/イベント統計データ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ca\卒研\Event Day\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B166E9D3-9791-4B8C-AF80-EE25DE82B514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B370CC36-787C-417B-9A71-1B7E3FA7293F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3350" yWindow="1070" windowWidth="16200" windowHeight="10080" xr2:uid="{A6CF68C4-3B23-44CC-A8D2-418C0C662BC4}"/>
+    <workbookView xWindow="3000" yWindow="0" windowWidth="16200" windowHeight="10080" xr2:uid="{A6CF68C4-3B23-44CC-A8D2-418C0C662BC4}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="118">
   <si>
     <t>2024年～2026年台湾プロ野球各球団のイベントデー集計</t>
     <rPh sb="4" eb="5">
@@ -292,6 +292,9 @@
       <t>コウハンセン</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中信ブラザーズ</t>
   </si>
   <si>
     <t>中信ブラザーズ</t>
@@ -533,6 +536,378 @@
     <t>超萌IP聯寵物日 Pingu</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>【奪還 だっかん】2026中信兄弟主場開幕戰</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歡迎光臨巧虎SWEET LAND</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SNOOPY &amp; HIS SIBLINGS A JOUNERY TOGETHER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第13屆我不是歌手：THE SHINE BEGINS！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ChannelB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」棒球音樂祭</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全效出擊，主宰全場！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍角散</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Colgate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>前進洲際~ GIABBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>’</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>S CHALLENGE~</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PEANUTS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>涼水祭 Bro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>’s Water Park</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aape</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TAICHUNG BROS CITY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>守護你的星</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Power Puff Girls</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>Let</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'s Race！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>洲際大奬賽</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RACING TEAM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>House 好侍</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ya Haw！Eddy 牛仔歷險記</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鬼滅の刃</t>
+    <rPh sb="0" eb="2">
+      <t>キメツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヤイバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>決戰無限城</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歷史一刻！台北大巨蛋開戰</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>花漾天母</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小龍女主場秀</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乖乖野球開唱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Poli親子毛孩日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>王道龍星大樂</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>品客FUN開玩</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>搖頭公仔之夜</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天母棒球場</t>
+  </si>
+  <si>
+    <t>《暗黑破壞神IV：憎恨之軀》</t>
+  </si>
+  <si>
+    <t>花蓮德興棒球場</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大叔乾一杯</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原裝上陣</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>緯來復古日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>海灘之約女孩日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トランスフォーマー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>變形金剛 - 龍巢之戰</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新光之Sing狂歡節</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SEGA遊樂場</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天母棒球場</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味全龍主場開幕戰</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍學院運動會</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>香香派對</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍星大樂</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全家冰料野球開唱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB SHOW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>甜點派對女子孩日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>侏羅紀世界：重生</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍寶貝親子日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍魂復古日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hololive night</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>林智勝引退系列賽</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JOGUMAN WITH DRAGONS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RUN &amp; ROAR 奔龍而上</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開幕系列戰</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍學院迎新日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Batter Up, Buckle Up 亞洲領航，氣勢如紅！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍之萌友的應援時光</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍總為了生活</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tasting the World達美樂世界風味季</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>Domino</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>'s</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -541,7 +916,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,6 +953,14 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -601,7 +984,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -612,6 +995,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -639,12 +1028,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}" name="EventSummary" displayName="EventSummary" ref="A2:I58" totalsRowShown="0">
-  <autoFilter ref="A2:I58" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}" name="EventSummary" displayName="EventSummary" ref="A2:I173" totalsRowShown="0">
+  <autoFilter ref="A2:I173" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{E394152D-5251-42F2-BBA6-4EC4F2D9A954}" name="球団"/>
-    <tableColumn id="2" xr3:uid="{34B3AD93-C8CB-42CC-91C6-D60735EAC90E}" name="年月日" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{860E6FF3-7022-4C6F-B9B7-6B4EB6509D1B}" name="シーズン" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{860E6FF3-7022-4C6F-B9B7-6B4EB6509D1B}" name="シーズン" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{34B3AD93-C8CB-42CC-91C6-D60735EAC90E}" name="年月日" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{17EC21EA-E31F-4527-98DD-D196942E795D}" name="対戦相手"/>
     <tableColumn id="7" xr3:uid="{F6D5D400-D300-4F98-8BB2-591905FE1FFC}" name="スタジアム"/>
     <tableColumn id="4" xr3:uid="{FB090584-30CC-4B9B-8EB4-81189F638591}" name="イベント名"/>
@@ -963,18 +1352,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FFA7CF5-486E-4A81-908D-5B6B06AA399E}">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="11.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -987,13 +1374,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -1018,14 +1405,14 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="1">
         <v>45385</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>22</v>
@@ -1034,7 +1421,7 @@
         <v>8</v>
       </c>
       <c r="L3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M3" t="s">
         <v>29</v>
@@ -1044,14 +1431,14 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="1">
         <v>45386</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>22</v>
@@ -1060,7 +1447,7 @@
         <v>8</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M4" t="s">
         <v>30</v>
@@ -1070,14 +1457,14 @@
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1">
         <v>45395</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -1086,21 +1473,21 @@
         <v>9</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="1">
         <v>45396</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -1109,21 +1496,21 @@
         <v>9</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="1">
         <v>45409</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -1132,21 +1519,21 @@
         <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1">
         <v>45410</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -1155,21 +1542,21 @@
         <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1">
         <v>45416</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -1182,14 +1569,14 @@
       <c r="A10" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1">
         <v>45417</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -1202,14 +1589,14 @@
       <c r="A11" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1">
         <v>45430</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
@@ -1222,14 +1609,14 @@
       <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1">
         <v>45431</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
@@ -1242,14 +1629,14 @@
       <c r="A13" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1">
         <v>45451</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
@@ -1262,14 +1649,14 @@
       <c r="A14" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1">
         <v>45452</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
@@ -1282,14 +1669,14 @@
       <c r="A15" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1">
         <v>45458</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>22</v>
@@ -1302,14 +1689,14 @@
       <c r="A16" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1">
         <v>45459</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>22</v>
@@ -1322,14 +1709,14 @@
       <c r="A17" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1">
         <v>45486</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
         <v>21</v>
@@ -1342,14 +1729,14 @@
       <c r="A18" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="1">
         <v>45487</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
         <v>21</v>
@@ -1362,14 +1749,14 @@
       <c r="A19" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="1">
         <v>45507</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>22</v>
@@ -1382,14 +1769,14 @@
       <c r="A20" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="1">
         <v>45508</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>22</v>
@@ -1402,14 +1789,14 @@
       <c r="A21" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="1">
         <v>45517</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>23</v>
@@ -1422,14 +1809,14 @@
       <c r="A22" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="1">
         <v>45518</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>23</v>
@@ -1442,14 +1829,14 @@
       <c r="A23" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="1">
         <v>45521</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
         <v>21</v>
@@ -1462,14 +1849,14 @@
       <c r="A24" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="1">
         <v>45522</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
         <v>21</v>
@@ -1482,14 +1869,14 @@
       <c r="A25" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="1">
         <v>45528</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E25" t="s">
         <v>21</v>
@@ -1502,14 +1889,14 @@
       <c r="A26" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="1">
         <v>45529</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E26" t="s">
         <v>21</v>
@@ -1522,14 +1909,14 @@
       <c r="A27" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="1">
         <v>45542</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
         <v>21</v>
@@ -1542,14 +1929,14 @@
       <c r="A28" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="1">
         <v>45543</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
         <v>21</v>
@@ -1562,14 +1949,14 @@
       <c r="A29" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="1">
         <v>45556</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>22</v>
@@ -1582,14 +1969,14 @@
       <c r="A30" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="1">
         <v>45557</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>22</v>
@@ -1602,14 +1989,14 @@
       <c r="A31" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="1">
         <v>45745</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>22</v>
@@ -1622,14 +2009,14 @@
       <c r="A32" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="1">
         <v>45746</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>22</v>
@@ -1642,14 +2029,14 @@
       <c r="A33" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="1">
         <v>45751</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s">
         <v>21</v>
@@ -1662,14 +2049,14 @@
       <c r="A34" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="1">
         <v>45752</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E34" t="s">
         <v>21</v>
@@ -1682,14 +2069,14 @@
       <c r="A35" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="1">
         <v>45753</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E35" t="s">
         <v>21</v>
@@ -1702,14 +2089,14 @@
       <c r="A36" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="1">
         <v>45766</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>22</v>
@@ -1722,14 +2109,14 @@
       <c r="A37" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="1">
         <v>45767</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>22</v>
@@ -1742,450 +2129,2752 @@
       <c r="A38" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="1">
         <v>45787</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E38" t="s">
         <v>21</v>
       </c>
       <c r="F38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="1">
         <v>45788</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E39" t="s">
         <v>21</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="1">
         <v>45794</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E40" t="s">
         <v>21</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="1">
         <v>45795</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E41" t="s">
         <v>21</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="1">
         <v>45807</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E42" t="s">
         <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="1">
         <v>45808</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E43" t="s">
         <v>21</v>
       </c>
       <c r="F43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="1">
         <v>45809</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E44" t="s">
         <v>21</v>
       </c>
       <c r="F44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" s="1">
         <v>45829</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E45" t="s">
         <v>21</v>
       </c>
       <c r="F45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" s="1">
         <v>45830</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E46" t="s">
         <v>21</v>
       </c>
       <c r="F46" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" s="1">
         <v>45850</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E47" t="s">
         <v>21</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>6</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="1">
         <v>45851</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E48" t="s">
         <v>21</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>6</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="1">
         <v>45871</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D49" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" s="1">
         <v>45872</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>6</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="1">
         <v>45878</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E51" t="s">
         <v>21</v>
       </c>
       <c r="F51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>6</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="1">
         <v>45879</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E52" t="s">
         <v>21</v>
       </c>
       <c r="F52" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>6</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="1">
         <v>45892</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="1">
         <v>45893</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>6</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="1">
         <v>45906</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E55" t="s">
         <v>21</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>6</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="1">
         <v>46272</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E56" t="s">
         <v>21</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>6</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="1">
         <v>45920</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E57" t="s">
         <v>21</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="1">
         <v>45921</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E58" t="s">
         <v>21</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" s="1">
+        <v>46110</v>
+      </c>
+      <c r="D59" t="s">
+        <v>36</v>
+      </c>
+      <c r="E59" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="1">
+        <v>46115</v>
+      </c>
+      <c r="D60" t="s">
+        <v>47</v>
+      </c>
+      <c r="E60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" s="1">
+        <v>46116</v>
+      </c>
+      <c r="D61" t="s">
+        <v>47</v>
+      </c>
+      <c r="E61" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" s="1">
+        <v>46117</v>
+      </c>
+      <c r="D62" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" s="1">
+        <v>46137</v>
+      </c>
+      <c r="D63" t="s">
+        <v>36</v>
+      </c>
+      <c r="E63" t="s">
+        <v>21</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" s="1">
+        <v>46138</v>
+      </c>
+      <c r="D64" t="s">
+        <v>36</v>
+      </c>
+      <c r="E64" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D65" t="s">
+        <v>34</v>
+      </c>
+      <c r="E65" t="s">
+        <v>21</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" s="1">
+        <v>46151</v>
+      </c>
+      <c r="D66" t="s">
+        <v>34</v>
+      </c>
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="1">
+        <v>46152</v>
+      </c>
+      <c r="D67" t="s">
+        <v>34</v>
+      </c>
+      <c r="E67" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D68" t="s">
+        <v>38</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F68" t="s">
+        <v>60</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D69" t="s">
+        <v>38</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" t="s">
+        <v>60</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D70" t="s">
+        <v>38</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F70" t="s">
+        <v>60</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" t="s">
+        <v>6</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D71" t="s">
+        <v>33</v>
+      </c>
+      <c r="E71" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" t="s">
+        <v>61</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D72" t="s">
+        <v>33</v>
+      </c>
+      <c r="E72" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" t="s">
+        <v>61</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" t="s">
+        <v>6</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D73" t="s">
+        <v>33</v>
+      </c>
+      <c r="E73" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" s="1">
+        <v>46187</v>
+      </c>
+      <c r="D74" t="s">
+        <v>33</v>
+      </c>
+      <c r="E74" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" s="1">
+        <v>46207</v>
+      </c>
+      <c r="D75" t="s">
+        <v>33</v>
+      </c>
+      <c r="E75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C76" s="1">
+        <v>46208</v>
+      </c>
+      <c r="D76" t="s">
+        <v>33</v>
+      </c>
+      <c r="E76" t="s">
+        <v>21</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="1">
+        <v>46228</v>
+      </c>
+      <c r="D77" t="s">
+        <v>47</v>
+      </c>
+      <c r="E77" t="s">
+        <v>21</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" s="1">
+        <v>46229</v>
+      </c>
+      <c r="D78" t="s">
+        <v>47</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C79" s="1">
+        <v>46249</v>
+      </c>
+      <c r="D79" t="s">
+        <v>34</v>
+      </c>
+      <c r="E79" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="1">
+        <v>46250</v>
+      </c>
+      <c r="D80" t="s">
+        <v>34</v>
+      </c>
+      <c r="E80" t="s">
+        <v>21</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81" s="1">
+        <v>46263</v>
+      </c>
+      <c r="D81" t="s">
+        <v>36</v>
+      </c>
+      <c r="E81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C82" s="1">
+        <v>46264</v>
+      </c>
+      <c r="D82" t="s">
+        <v>36</v>
+      </c>
+      <c r="E82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" s="1">
+        <v>46270</v>
+      </c>
+      <c r="D83" t="s">
+        <v>38</v>
+      </c>
+      <c r="E83" t="s">
+        <v>21</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="1">
+        <v>46271</v>
+      </c>
+      <c r="D84" t="s">
+        <v>38</v>
+      </c>
+      <c r="E84" t="s">
+        <v>21</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" s="1">
+        <v>46283</v>
+      </c>
+      <c r="D85" t="s">
+        <v>47</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F85" t="s">
+        <v>76</v>
+      </c>
+      <c r="H85" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C86" s="1">
+        <v>46284</v>
+      </c>
+      <c r="D86" t="s">
+        <v>38</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F86" t="s">
+        <v>76</v>
+      </c>
+      <c r="H86" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C87" s="1">
+        <v>46285</v>
+      </c>
+      <c r="D87" t="s">
+        <v>38</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F87" t="s">
+        <v>76</v>
+      </c>
+      <c r="H87" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" t="s">
+        <v>38</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" s="1">
+        <v>45381</v>
+      </c>
+      <c r="D88" t="s">
+        <v>33</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" t="s">
+        <v>38</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" s="1">
+        <v>45382</v>
+      </c>
+      <c r="D89" t="s">
+        <v>33</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" t="s">
+        <v>38</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C90" s="1">
+        <v>45387</v>
+      </c>
+      <c r="D90" t="s">
+        <v>47</v>
+      </c>
+      <c r="E90" t="s">
+        <v>85</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" t="s">
+        <v>38</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C91" s="1">
+        <v>45388</v>
+      </c>
+      <c r="D91" t="s">
+        <v>47</v>
+      </c>
+      <c r="E91" t="s">
+        <v>85</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" t="s">
+        <v>38</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" s="1">
+        <v>45389</v>
+      </c>
+      <c r="D92" t="s">
+        <v>47</v>
+      </c>
+      <c r="E92" t="s">
+        <v>85</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" t="s">
+        <v>38</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" s="1">
+        <v>45401</v>
+      </c>
+      <c r="D93" t="s">
+        <v>33</v>
+      </c>
+      <c r="E93" t="s">
+        <v>85</v>
+      </c>
+      <c r="F93" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" t="s">
+        <v>38</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" s="1">
+        <v>45402</v>
+      </c>
+      <c r="D94" t="s">
+        <v>33</v>
+      </c>
+      <c r="E94" t="s">
+        <v>85</v>
+      </c>
+      <c r="F94" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" t="s">
+        <v>38</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C95" s="1">
+        <v>45403</v>
+      </c>
+      <c r="D95" t="s">
+        <v>33</v>
+      </c>
+      <c r="E95" t="s">
+        <v>85</v>
+      </c>
+      <c r="F95" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
+        <v>38</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96" s="1">
+        <v>45416</v>
+      </c>
+      <c r="D96" t="s">
+        <v>34</v>
+      </c>
+      <c r="E96" t="s">
+        <v>85</v>
+      </c>
+      <c r="F96" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" t="s">
+        <v>38</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97" s="1">
+        <v>45417</v>
+      </c>
+      <c r="D97" t="s">
+        <v>34</v>
+      </c>
+      <c r="E97" t="s">
+        <v>85</v>
+      </c>
+      <c r="F97" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" t="s">
+        <v>38</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" s="1">
+        <v>45430</v>
+      </c>
+      <c r="D98" t="s">
+        <v>36</v>
+      </c>
+      <c r="E98" t="s">
+        <v>85</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" t="s">
+        <v>38</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" s="1">
+        <v>45431</v>
+      </c>
+      <c r="D99" t="s">
+        <v>36</v>
+      </c>
+      <c r="E99" t="s">
+        <v>85</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" t="s">
+        <v>38</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" s="1">
+        <v>45443</v>
+      </c>
+      <c r="D100" t="s">
+        <v>33</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" t="s">
+        <v>38</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C101" s="1">
+        <v>45444</v>
+      </c>
+      <c r="D101" t="s">
+        <v>33</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" t="s">
+        <v>38</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C102" s="1">
+        <v>45445</v>
+      </c>
+      <c r="D102" t="s">
+        <v>33</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" t="s">
+        <v>38</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C103" s="1">
+        <v>45458</v>
+      </c>
+      <c r="D103" t="s">
+        <v>33</v>
+      </c>
+      <c r="E103" t="s">
+        <v>85</v>
+      </c>
+      <c r="F103" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" t="s">
+        <v>38</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C104" s="1">
+        <v>45459</v>
+      </c>
+      <c r="D104" t="s">
+        <v>33</v>
+      </c>
+      <c r="E104" t="s">
+        <v>85</v>
+      </c>
+      <c r="F104" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" t="s">
+        <v>38</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C105" s="1">
+        <v>45461</v>
+      </c>
+      <c r="D105" t="s">
+        <v>34</v>
+      </c>
+      <c r="E105" t="s">
+        <v>85</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" t="s">
+        <v>38</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C106" s="1">
+        <v>45463</v>
+      </c>
+      <c r="D106" t="s">
+        <v>31</v>
+      </c>
+      <c r="E106" t="s">
+        <v>85</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" t="s">
+        <v>38</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107" s="1">
+        <v>45464</v>
+      </c>
+      <c r="D107" t="s">
+        <v>31</v>
+      </c>
+      <c r="E107" t="s">
+        <v>85</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" t="s">
+        <v>38</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C108" s="1">
+        <v>45479</v>
+      </c>
+      <c r="D108" t="s">
+        <v>34</v>
+      </c>
+      <c r="E108" t="s">
+        <v>85</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" t="s">
+        <v>38</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C109" s="1">
+        <v>45480</v>
+      </c>
+      <c r="D109" t="s">
+        <v>34</v>
+      </c>
+      <c r="E109" t="s">
+        <v>85</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" t="s">
+        <v>38</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C110" s="1">
+        <v>45506</v>
+      </c>
+      <c r="D110" t="s">
+        <v>33</v>
+      </c>
+      <c r="E110" t="s">
+        <v>87</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" t="s">
+        <v>38</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C111" s="1">
+        <v>45507</v>
+      </c>
+      <c r="D111" t="s">
+        <v>33</v>
+      </c>
+      <c r="E111" t="s">
+        <v>87</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" t="s">
+        <v>38</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C112" s="1">
+        <v>45508</v>
+      </c>
+      <c r="D112" t="s">
+        <v>33</v>
+      </c>
+      <c r="E112" t="s">
+        <v>87</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" t="s">
+        <v>38</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C113" s="1">
+        <v>45520</v>
+      </c>
+      <c r="D113" t="s">
+        <v>36</v>
+      </c>
+      <c r="E113" t="s">
+        <v>85</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" t="s">
+        <v>38</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C114" s="1">
+        <v>45521</v>
+      </c>
+      <c r="D114" t="s">
+        <v>36</v>
+      </c>
+      <c r="E114" t="s">
+        <v>85</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" t="s">
+        <v>38</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C115" s="1">
+        <v>45522</v>
+      </c>
+      <c r="D115" t="s">
+        <v>36</v>
+      </c>
+      <c r="E115" t="s">
+        <v>85</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" t="s">
+        <v>38</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C116" s="1">
+        <v>45534</v>
+      </c>
+      <c r="D116" t="s">
+        <v>47</v>
+      </c>
+      <c r="E116" t="s">
+        <v>85</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" t="s">
+        <v>38</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C117" s="1">
+        <v>45535</v>
+      </c>
+      <c r="D117" t="s">
+        <v>47</v>
+      </c>
+      <c r="E117" t="s">
+        <v>85</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" t="s">
+        <v>38</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C118" s="1">
+        <v>45536</v>
+      </c>
+      <c r="D118" t="s">
+        <v>47</v>
+      </c>
+      <c r="E118" t="s">
+        <v>85</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" t="s">
+        <v>38</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C119" s="1">
+        <v>45549</v>
+      </c>
+      <c r="D119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H119" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" t="s">
+        <v>38</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" s="1">
+        <v>45550</v>
+      </c>
+      <c r="D120" t="s">
+        <v>31</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H120" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" t="s">
+        <v>38</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C121" s="1">
+        <v>45551</v>
+      </c>
+      <c r="D121" t="s">
+        <v>31</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" t="s">
+        <v>38</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122" s="1">
+        <v>45552</v>
+      </c>
+      <c r="D122" t="s">
+        <v>34</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" t="s">
+        <v>38</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C123" s="1">
+        <v>45563</v>
+      </c>
+      <c r="D123" t="s">
+        <v>36</v>
+      </c>
+      <c r="E123" t="s">
+        <v>85</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" t="s">
+        <v>38</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C124" s="1">
+        <v>45564</v>
+      </c>
+      <c r="D124" t="s">
+        <v>36</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F124" t="s">
+        <v>86</v>
+      </c>
+      <c r="H124" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" t="s">
+        <v>38</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C125" s="1">
+        <v>45749</v>
+      </c>
+      <c r="D125" t="s">
+        <v>34</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" t="s">
+        <v>38</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C126" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D126" t="s">
+        <v>34</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" t="s">
+        <v>38</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C127" s="1">
+        <v>45751</v>
+      </c>
+      <c r="D127" t="s">
+        <v>36</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" t="s">
+        <v>38</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C128" s="1">
+        <v>45752</v>
+      </c>
+      <c r="D128" t="s">
+        <v>36</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" t="s">
+        <v>38</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C129" s="1">
+        <v>45753</v>
+      </c>
+      <c r="D129" t="s">
+        <v>36</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" t="s">
+        <v>38</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C130" s="1">
+        <v>45772</v>
+      </c>
+      <c r="D130" t="s">
+        <v>47</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" t="s">
+        <v>38</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C131" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D131" t="s">
+        <v>47</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" t="s">
+        <v>38</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C132" s="1">
+        <v>45774</v>
+      </c>
+      <c r="D132" t="s">
+        <v>47</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" t="s">
+        <v>38</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C133" s="1">
+        <v>45787</v>
+      </c>
+      <c r="D133" t="s">
+        <v>33</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" t="s">
+        <v>38</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C134" s="1">
+        <v>45788</v>
+      </c>
+      <c r="D134" t="s">
+        <v>33</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A135" t="s">
+        <v>38</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C135" s="1">
+        <v>45800</v>
+      </c>
+      <c r="D135" t="s">
+        <v>34</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" t="s">
+        <v>38</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C136" s="1">
+        <v>45801</v>
+      </c>
+      <c r="D136" t="s">
+        <v>34</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" t="s">
+        <v>38</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C137" s="1">
+        <v>45802</v>
+      </c>
+      <c r="D137" t="s">
+        <v>34</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A138" t="s">
+        <v>38</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C138" s="1">
+        <v>45815</v>
+      </c>
+      <c r="D138" t="s">
+        <v>47</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A139" t="s">
+        <v>38</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C139" s="1">
+        <v>45816</v>
+      </c>
+      <c r="D139" t="s">
+        <v>47</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A140" t="s">
+        <v>38</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C140" s="1">
+        <v>45829</v>
+      </c>
+      <c r="D140" t="s">
+        <v>47</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A141" t="s">
+        <v>38</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C141" s="1">
+        <v>45830</v>
+      </c>
+      <c r="D141" t="s">
+        <v>47</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A142" t="s">
+        <v>38</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C142" s="1">
+        <v>45842</v>
+      </c>
+      <c r="D142" t="s">
+        <v>47</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A143" t="s">
+        <v>38</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C143" s="1">
+        <v>45843</v>
+      </c>
+      <c r="D143" t="s">
+        <v>47</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A144" t="s">
+        <v>38</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C144" s="1">
+        <v>45844</v>
+      </c>
+      <c r="D144" t="s">
+        <v>47</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" t="s">
+        <v>38</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C145" s="1">
+        <v>45864</v>
+      </c>
+      <c r="D145" t="s">
+        <v>36</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F145" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A146" t="s">
+        <v>38</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C146" s="1">
+        <v>45865</v>
+      </c>
+      <c r="D146" t="s">
+        <v>36</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F146" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A147" t="s">
+        <v>38</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C147" s="1">
+        <v>45885</v>
+      </c>
+      <c r="D147" t="s">
+        <v>33</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A148" t="s">
+        <v>38</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C148" s="1">
+        <v>45886</v>
+      </c>
+      <c r="D148" t="s">
+        <v>33</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A149" t="s">
+        <v>38</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C149" s="1">
+        <v>45895</v>
+      </c>
+      <c r="D149" t="s">
+        <v>47</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A150" t="s">
+        <v>38</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150" s="1">
+        <v>45896</v>
+      </c>
+      <c r="D150" t="s">
+        <v>47</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A151" t="s">
+        <v>38</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C151" s="1">
+        <v>45898</v>
+      </c>
+      <c r="D151" t="s">
+        <v>31</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A152" t="s">
+        <v>38</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C152" s="1">
+        <v>45899</v>
+      </c>
+      <c r="D152" t="s">
+        <v>31</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A153" t="s">
+        <v>38</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C153" s="1">
+        <v>45900</v>
+      </c>
+      <c r="D153" t="s">
+        <v>31</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A154" t="s">
+        <v>38</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C154" s="1">
+        <v>45905</v>
+      </c>
+      <c r="D154" t="s">
+        <v>34</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A155" t="s">
+        <v>38</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C155" s="1">
+        <v>45906</v>
+      </c>
+      <c r="D155" t="s">
+        <v>34</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A156" t="s">
+        <v>38</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C156" s="1">
+        <v>45907</v>
+      </c>
+      <c r="D156" t="s">
+        <v>34</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A157" t="s">
+        <v>38</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C157" s="1">
+        <v>45927</v>
+      </c>
+      <c r="D157" t="s">
+        <v>36</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" t="s">
+        <v>38</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C158" s="1">
+        <v>45928</v>
+      </c>
+      <c r="D158" t="s">
+        <v>36</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159" t="s">
+        <v>38</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C159" s="1">
+        <v>46115</v>
+      </c>
+      <c r="D159" t="s">
+        <v>34</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B160" s="1"/>
+      <c r="C160" s="1">
+        <v>46116</v>
+      </c>
+      <c r="D160" t="s">
+        <v>34</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="161" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B161" s="1"/>
+      <c r="C161" s="1">
+        <v>46117</v>
+      </c>
+      <c r="D161" t="s">
+        <v>34</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="162" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B162" s="1"/>
+      <c r="C162" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D162" t="s">
+        <v>33</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="163" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B163" s="1"/>
+      <c r="C163" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D163" t="s">
+        <v>33</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="164" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B164" s="1"/>
+      <c r="C164" s="1">
+        <v>46129</v>
+      </c>
+      <c r="D164" t="s">
+        <v>31</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="165" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B165" s="1"/>
+      <c r="C165" s="1">
+        <v>46130</v>
+      </c>
+      <c r="D165" t="s">
+        <v>31</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="166" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B166" s="1"/>
+      <c r="C166" s="1">
+        <v>46131</v>
+      </c>
+      <c r="D166" t="s">
+        <v>31</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="167" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B167" s="1"/>
+      <c r="C167" s="1">
+        <v>46144</v>
+      </c>
+      <c r="D167" t="s">
+        <v>36</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="168" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B168" s="1"/>
+      <c r="C168" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D168" t="s">
+        <v>36</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="169" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B169" s="1"/>
+      <c r="C169" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D169" t="s">
+        <v>31</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="170" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B170" s="1"/>
+      <c r="C170" s="1">
+        <v>46148</v>
+      </c>
+      <c r="D170" t="s">
+        <v>31</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="171" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B171" s="1"/>
+      <c r="C171" s="1">
+        <v>46157</v>
+      </c>
+      <c r="D171" t="s">
+        <v>33</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="172" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B172" s="1"/>
+      <c r="C172" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D172" t="s">
+        <v>33</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="173" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B173" s="1"/>
+      <c r="C173" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D173" t="s">
+        <v>33</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A58" xr:uid="{AE6A38C0-572D-4047-B9F9-1FC7841EE013}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A173" xr:uid="{AE6A38C0-572D-4047-B9F9-1FC7841EE013}">
       <formula1>$L$2:$L$8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C58" xr:uid="{4EFB52BD-777A-49C0-AB2C-CA7A84FB8040}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B173" xr:uid="{4EFB52BD-777A-49C0-AB2C-CA7A84FB8040}">
       <formula1>$M$3:$M$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{E06B60E4-D0A3-4733-BC22-8A777CB2F035}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D173" xr:uid="{E06B60E4-D0A3-4733-BC22-8A777CB2F035}">
       <formula1>$L$3:$L$8</formula1>
     </dataValidation>
   </dataValidations>

--- a/イベント統計データ.xlsx
+++ b/イベント統計データ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ca\卒研\Event Day\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B370CC36-787C-417B-9A71-1B7E3FA7293F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70056101-8F5C-4C66-90C8-B8C88F6203ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3000" yWindow="0" windowWidth="16200" windowHeight="10080" xr2:uid="{A6CF68C4-3B23-44CC-A8D2-418C0C662BC4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="205">
   <si>
     <t>2024年～2026年台湾プロ野球各球団のイベントデー集計</t>
     <rPh sb="4" eb="5">
@@ -220,15 +220,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>台中洲際棒球場</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>台北大巨蛋</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>台東第一棒球場</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -760,16 +752,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>天母棒球場</t>
-  </si>
-  <si>
     <t>《暗黑破壞神IV：憎恨之軀》</t>
   </si>
   <si>
-    <t>花蓮德興棒球場</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>大叔乾一杯</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -799,10 +784,6 @@
   </si>
   <si>
     <t>SEGA遊樂場</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>天母棒球場</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -908,6 +889,471 @@
     </r>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>Red！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가자！</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LG TWINS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔女的盛宴 DB SHOW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>台新新光金控</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>守護妳的EVE 心動方程式女孩日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>諾貝爾眼科</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hololive</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新光亞洲音樂祭</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新光人壽</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>85forever</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Beyond the Dragons Roar 龍星大樂</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>王道銀行</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>鷹祭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>SUMMER BOOST</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HUNTERxHUNTER 獵人</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HUNTERxHUNTER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Domino's</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>搖滾撞野球復古日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乖乖</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夠悍 GO STRONGER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小小世界</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重裝戰將</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>浪漫事務所</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悍將中學</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>萌萌PET隊</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有好市場</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>わくわく日本祭</t>
+    <rPh sb="4" eb="6">
+      <t>ニッポン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戀戀夏日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>G！POP流行音樂節</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>征戰野球</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> GUARDIANS</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STRONG 逐夢無限</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>寵愛天使</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>好樂派對</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FiGHT FOR ALL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奇趣城堡</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>春日探險 Adventure</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안녕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你好</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>心動信號</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>迺夜市呷好味</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>熱力製造所</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夏夜看球趣</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野球搜查線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>XVII悍將中學</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>虎道同盟</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BLUE POWER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ONE FOR ALL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LU來LU快樂</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>愛戀邱比特</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Skater JOHN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>城堡密語</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>POWER NIGHT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>旅行趣</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進擊的巨人</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進撃の巨人</t>
+    <rPh sb="0" eb="2">
+      <t>シンゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョジン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鷹元年世代</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ASE TSG DAY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ASE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高雄製造</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>南人祭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> Southern Festival</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>南國平原</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鷹Your Heart</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D-Link, Star Travel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ALL in 鷹</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>証券, 病院</t>
+    <rPh sb="0" eb="2">
+      <t>ショウケン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ビョウイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雄好宅</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発会社</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>心動時刻</t>
+  </si>
+  <si>
+    <t>心動時刻</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全球人壽, 証券</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鷹勇戰士</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FALA正港鷹雄</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>覺祭多巴胺</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体育協会</t>
+    <rPh sb="0" eb="2">
+      <t>タイイク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>台中洲際</t>
+  </si>
+  <si>
+    <t>台東第一</t>
+  </si>
+  <si>
+    <t>天母</t>
+  </si>
+  <si>
+    <t>花蓮德興</t>
+  </si>
+  <si>
+    <t>新莊</t>
+  </si>
+  <si>
+    <t>澄清湖</t>
+  </si>
+  <si>
+    <t>翅膀硬了！！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高雄製造浪漫</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>南人祭 Southern Festival</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>來Kid Takao家</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雄鷹戰將煞猛拚</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鷹樂將</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>清香出擊</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明星花露水</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正港鷹雄</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>做伴拚</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動物群鷹會！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>熱力製造所闘雙城南人祭</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鷹浪 做伴使勁搖</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TAKAO與他的好友出遊趣</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -916,7 +1362,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -961,6 +1407,27 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -970,11 +1437,35 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -984,7 +1475,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1001,6 +1492,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1028,8 +1537,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}" name="EventSummary" displayName="EventSummary" ref="A2:I173" totalsRowShown="0">
-  <autoFilter ref="A2:I173" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}" name="EventSummary" displayName="EventSummary" ref="A2:I355" totalsRowShown="0">
+  <autoFilter ref="A2:I355" xr:uid="{48668E31-0BC0-438F-A8F5-E4964BDD2218}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{E394152D-5251-42F2-BBA6-4EC4F2D9A954}" name="球団"/>
     <tableColumn id="10" xr3:uid="{860E6FF3-7022-4C6F-B9B7-6B4EB6509D1B}" name="シーズン" dataDxfId="1"/>
@@ -1352,13 +1861,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FFA7CF5-486E-4A81-908D-5B6B06AA399E}">
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M355"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="11.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" customWidth="1"/>
     <col min="5" max="6" width="14.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.5" customWidth="1"/>
     <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
@@ -1374,13 +1883,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -1392,7 +1901,7 @@
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
         <v>4</v>
@@ -1406,25 +1915,25 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1">
         <v>45385</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
       </c>
       <c r="L3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1432,25 +1941,25 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1">
         <v>45386</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1458,22 +1967,22 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1">
         <v>45395</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1481,22 +1990,22 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1">
         <v>45396</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1504,22 +2013,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1">
         <v>45409</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1527,22 +2036,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1">
         <v>45410</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1550,16 +2059,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1">
         <v>45416</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>10</v>
@@ -1570,16 +2079,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1">
         <v>45417</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>10</v>
@@ -1590,16 +2099,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1">
         <v>45430</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -1610,16 +2119,16 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" s="1">
         <v>45431</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -1630,16 +2139,16 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13" s="1">
         <v>45451</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -1650,16 +2159,16 @@
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1">
         <v>45452</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -1670,16 +2179,16 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1">
         <v>45458</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -1690,16 +2199,16 @@
         <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1">
         <v>45459</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -1710,16 +2219,16 @@
         <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1">
         <v>45486</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>14</v>
@@ -1730,16 +2239,16 @@
         <v>6</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1">
         <v>45487</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>14</v>
@@ -1750,16 +2259,16 @@
         <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C19" s="1">
         <v>45507</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>15</v>
@@ -1770,16 +2279,16 @@
         <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1">
         <v>45508</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>15</v>
@@ -1790,16 +2299,16 @@
         <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1">
         <v>45517</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="E21" t="s">
+        <v>186</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>16</v>
@@ -1810,16 +2319,16 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1">
         <v>45518</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="E22" t="s">
+        <v>186</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>16</v>
@@ -1830,16 +2339,16 @@
         <v>6</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1">
         <v>45521</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>17</v>
@@ -1850,16 +2359,16 @@
         <v>6</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1">
         <v>45522</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>17</v>
@@ -1870,16 +2379,16 @@
         <v>6</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1">
         <v>45528</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>17</v>
@@ -1890,16 +2399,16 @@
         <v>6</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1">
         <v>45529</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>17</v>
@@ -1910,16 +2419,16 @@
         <v>6</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C27" s="1">
         <v>45542</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -1930,16 +2439,16 @@
         <v>6</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C28" s="1">
         <v>45543</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
@@ -1950,16 +2459,16 @@
         <v>6</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C29" s="1">
         <v>45556</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="E29" t="s">
+        <v>21</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -1970,16 +2479,16 @@
         <v>6</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C30" s="1">
         <v>45557</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="E30" t="s">
+        <v>21</v>
       </c>
       <c r="F30" t="s">
         <v>20</v>
@@ -1990,19 +2499,19 @@
         <v>6</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C31" s="1">
         <v>45745</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" t="s">
         <v>22</v>
-      </c>
-      <c r="F31" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2010,19 +2519,19 @@
         <v>6</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C32" s="1">
         <v>45746</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" t="s">
         <v>22</v>
-      </c>
-      <c r="F32" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2030,19 +2539,19 @@
         <v>6</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C33" s="1">
         <v>45751</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2050,19 +2559,19 @@
         <v>6</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1">
         <v>45752</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2070,19 +2579,19 @@
         <v>6</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C35" s="1">
         <v>45753</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2090,19 +2599,19 @@
         <v>6</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C36" s="1">
         <v>45766</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="E36" t="s">
+        <v>21</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2110,19 +2619,19 @@
         <v>6</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C37" s="1">
         <v>45767</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="E37" t="s">
+        <v>21</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2130,19 +2639,19 @@
         <v>6</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C38" s="1">
         <v>45787</v>
       </c>
       <c r="D38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2150,19 +2659,19 @@
         <v>6</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C39" s="1">
         <v>45788</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2170,19 +2679,19 @@
         <v>6</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C40" s="1">
         <v>45794</v>
       </c>
       <c r="D40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2190,19 +2699,19 @@
         <v>6</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C41" s="1">
         <v>45795</v>
       </c>
       <c r="D41" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2210,19 +2719,19 @@
         <v>6</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C42" s="1">
         <v>45807</v>
       </c>
       <c r="D42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F42" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2230,19 +2739,19 @@
         <v>6</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C43" s="1">
         <v>45808</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E43" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2250,19 +2759,19 @@
         <v>6</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C44" s="1">
         <v>45809</v>
       </c>
       <c r="D44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F44" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2270,19 +2779,19 @@
         <v>6</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C45" s="1">
         <v>45829</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E45" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2290,19 +2799,19 @@
         <v>6</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C46" s="1">
         <v>45830</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E46" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F46" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2310,19 +2819,19 @@
         <v>6</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C47" s="1">
         <v>45850</v>
       </c>
       <c r="D47" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2330,19 +2839,19 @@
         <v>6</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C48" s="1">
         <v>45851</v>
       </c>
       <c r="D48" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E48" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2350,19 +2859,19 @@
         <v>6</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C49" s="1">
         <v>45871</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E49" t="s">
+        <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2370,19 +2879,19 @@
         <v>6</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C50" s="1">
         <v>45872</v>
       </c>
       <c r="D50" t="s">
-        <v>33</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E50" t="s">
+        <v>21</v>
       </c>
       <c r="F50" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2390,19 +2899,19 @@
         <v>6</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C51" s="1">
         <v>45878</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E51" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F51" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2410,19 +2919,19 @@
         <v>6</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C52" s="1">
         <v>45879</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F52" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2430,22 +2939,22 @@
         <v>6</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C53" s="1">
         <v>45892</v>
       </c>
       <c r="D53" t="s">
-        <v>34</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E53" t="s">
+        <v>21</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2453,22 +2962,22 @@
         <v>6</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C54" s="1">
         <v>45893</v>
       </c>
       <c r="D54" t="s">
-        <v>34</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E54" t="s">
+        <v>21</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2476,22 +2985,22 @@
         <v>6</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C55" s="1">
         <v>45906</v>
       </c>
       <c r="D55" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2499,22 +3008,22 @@
         <v>6</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C56" s="1">
         <v>46272</v>
       </c>
       <c r="D56" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E56" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2522,22 +3031,22 @@
         <v>6</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C57" s="1">
         <v>45920</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2545,22 +3054,22 @@
         <v>6</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C58" s="1">
         <v>45921</v>
       </c>
       <c r="D58" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E58" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2568,19 +3077,19 @@
         <v>6</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C59" s="1">
         <v>46110</v>
       </c>
       <c r="D59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F59" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2588,19 +3097,19 @@
         <v>6</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C60" s="1">
         <v>46115</v>
       </c>
       <c r="D60" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E60" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2608,19 +3117,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C61" s="1">
         <v>46116</v>
       </c>
       <c r="D61" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2628,19 +3137,19 @@
         <v>6</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C62" s="1">
         <v>46117</v>
       </c>
       <c r="D62" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2648,22 +3157,22 @@
         <v>6</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C63" s="1">
         <v>46137</v>
       </c>
       <c r="D63" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E63" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2671,22 +3180,22 @@
         <v>6</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C64" s="1">
         <v>46138</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2694,19 +3203,19 @@
         <v>6</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C65" s="1">
         <v>46150</v>
       </c>
       <c r="D65" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2714,19 +3223,19 @@
         <v>6</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C66" s="1">
         <v>46151</v>
       </c>
       <c r="D66" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2734,19 +3243,19 @@
         <v>6</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C67" s="1">
         <v>46152</v>
       </c>
       <c r="D67" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E67" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2754,22 +3263,22 @@
         <v>6</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C68" s="1">
         <v>46164</v>
       </c>
       <c r="D68" t="s">
-        <v>38</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="E68" t="s">
+        <v>21</v>
       </c>
       <c r="F68" t="s">
+        <v>58</v>
+      </c>
+      <c r="H68" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2777,22 +3286,22 @@
         <v>6</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C69" s="1">
         <v>46165</v>
       </c>
       <c r="D69" t="s">
-        <v>38</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="E69" t="s">
+        <v>21</v>
       </c>
       <c r="F69" t="s">
+        <v>58</v>
+      </c>
+      <c r="H69" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2800,22 +3309,22 @@
         <v>6</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C70" s="1">
         <v>46166</v>
       </c>
       <c r="D70" t="s">
-        <v>38</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="E70" t="s">
+        <v>21</v>
       </c>
       <c r="F70" t="s">
+        <v>58</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2823,22 +3332,22 @@
         <v>6</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C71" s="1">
         <v>46179</v>
       </c>
       <c r="D71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F71" t="s">
+        <v>59</v>
+      </c>
+      <c r="H71" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2846,22 +3355,22 @@
         <v>6</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C72" s="1">
         <v>46180</v>
       </c>
       <c r="D72" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F72" t="s">
+        <v>59</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2869,19 +3378,19 @@
         <v>6</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C73" s="1">
         <v>46186</v>
       </c>
       <c r="D73" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2889,19 +3398,19 @@
         <v>6</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C74" s="1">
         <v>46187</v>
       </c>
       <c r="D74" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E74" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2909,19 +3418,19 @@
         <v>6</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C75" s="1">
         <v>46207</v>
       </c>
       <c r="D75" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E75" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2929,19 +3438,19 @@
         <v>6</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C76" s="1">
         <v>46208</v>
       </c>
       <c r="D76" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E76" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2949,22 +3458,22 @@
         <v>6</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C77" s="1">
         <v>46228</v>
       </c>
       <c r="D77" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E77" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2972,22 +3481,22 @@
         <v>6</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C78" s="1">
         <v>46229</v>
       </c>
       <c r="D78" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2995,22 +3504,22 @@
         <v>6</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C79" s="1">
         <v>46249</v>
       </c>
       <c r="D79" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E79" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3018,22 +3527,22 @@
         <v>6</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="1">
         <v>46250</v>
       </c>
       <c r="D80" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3041,22 +3550,22 @@
         <v>6</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C81" s="1">
         <v>46263</v>
       </c>
       <c r="D81" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E81" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3064,22 +3573,22 @@
         <v>6</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C82" s="1">
         <v>46264</v>
       </c>
       <c r="D82" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E82" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3087,22 +3596,22 @@
         <v>6</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C83" s="1">
         <v>46270</v>
       </c>
       <c r="D83" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E83" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3110,22 +3619,22 @@
         <v>6</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C84" s="1">
         <v>46271</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E84" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3133,22 +3642,22 @@
         <v>6</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C85" s="1">
         <v>46283</v>
       </c>
       <c r="D85" t="s">
-        <v>47</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
+      </c>
+      <c r="E85" t="s">
+        <v>21</v>
       </c>
       <c r="F85" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H85" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3156,22 +3665,22 @@
         <v>6</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C86" s="1">
         <v>46284</v>
       </c>
       <c r="D86" t="s">
-        <v>38</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="E86" t="s">
+        <v>21</v>
       </c>
       <c r="F86" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H86" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3179,1703 +3688,5557 @@
         <v>6</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C87" s="1">
         <v>46285</v>
       </c>
       <c r="D87" t="s">
-        <v>38</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="E87" t="s">
+        <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H87" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C88" s="1">
         <v>45381</v>
       </c>
       <c r="D88" t="s">
-        <v>33</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E88" t="s">
+        <v>21</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C89" s="1">
         <v>45382</v>
       </c>
       <c r="D89" t="s">
-        <v>33</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E89" t="s">
+        <v>21</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C90" s="1">
         <v>45387</v>
       </c>
       <c r="D90" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E90" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C91" s="1">
         <v>45388</v>
       </c>
       <c r="D91" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E91" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C92" s="1">
         <v>45389</v>
       </c>
       <c r="D92" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E92" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C93" s="1">
         <v>45401</v>
       </c>
       <c r="D93" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E93" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F93" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C94" s="1">
         <v>45402</v>
       </c>
       <c r="D94" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F94" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C95" s="1">
         <v>45403</v>
       </c>
       <c r="D95" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F95" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C96" s="1">
         <v>45416</v>
       </c>
       <c r="D96" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E96" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F96" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C97" s="1">
         <v>45417</v>
       </c>
       <c r="D97" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E97" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F97" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C98" s="1">
         <v>45430</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E98" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C99" s="1">
         <v>45431</v>
       </c>
       <c r="D99" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E99" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C100" s="1">
         <v>45443</v>
       </c>
       <c r="D100" t="s">
-        <v>33</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E100" t="s">
+        <v>21</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C101" s="1">
         <v>45444</v>
       </c>
       <c r="D101" t="s">
-        <v>33</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E101" t="s">
+        <v>21</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C102" s="1">
         <v>45445</v>
       </c>
       <c r="D102" t="s">
-        <v>33</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E102" t="s">
+        <v>21</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C103" s="1">
         <v>45458</v>
       </c>
       <c r="D103" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F103" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C104" s="1">
         <v>45459</v>
       </c>
       <c r="D104" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F104" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C105" s="1">
         <v>45461</v>
       </c>
       <c r="D105" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C106" s="1">
         <v>45463</v>
       </c>
       <c r="D106" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E106" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C107" s="1">
         <v>45464</v>
       </c>
       <c r="D107" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E107" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C108" s="1">
         <v>45479</v>
       </c>
       <c r="D108" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C109" s="1">
         <v>45480</v>
       </c>
       <c r="D109" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C110" s="1">
         <v>45506</v>
       </c>
       <c r="D110" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E110" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C111" s="1">
         <v>45507</v>
       </c>
       <c r="D111" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E111" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C112" s="1">
         <v>45508</v>
       </c>
       <c r="D112" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E112" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C113" s="1">
         <v>45520</v>
       </c>
       <c r="D113" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E113" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C114" s="1">
         <v>45521</v>
       </c>
       <c r="D114" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E114" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C115" s="1">
         <v>45522</v>
       </c>
       <c r="D115" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E115" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C116" s="1">
         <v>45534</v>
       </c>
       <c r="D116" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E116" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C117" s="1">
         <v>45535</v>
       </c>
       <c r="D117" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E117" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C118" s="1">
         <v>45536</v>
       </c>
       <c r="D118" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E118" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C119" s="1">
         <v>45549</v>
       </c>
       <c r="D119" t="s">
-        <v>31</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="E119" t="s">
+        <v>21</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H119" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C120" s="1">
         <v>45550</v>
       </c>
       <c r="D120" t="s">
-        <v>31</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="E120" t="s">
+        <v>21</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H120" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C121" s="1">
         <v>45551</v>
       </c>
       <c r="D121" t="s">
-        <v>31</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="E121" t="s">
+        <v>21</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C122" s="1">
         <v>45552</v>
       </c>
       <c r="D122" t="s">
-        <v>34</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E122" t="s">
+        <v>21</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C123" s="1">
         <v>45563</v>
       </c>
       <c r="D123" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E123" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C124" s="1">
         <v>45564</v>
       </c>
       <c r="D124" t="s">
-        <v>36</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="E124" t="s">
+        <v>21</v>
       </c>
       <c r="F124" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H124" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C125" s="1">
         <v>45749</v>
       </c>
       <c r="D125" t="s">
-        <v>34</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>96</v>
+        <v>32</v>
+      </c>
+      <c r="E125" t="s">
+        <v>187</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C126" s="1">
         <v>45750</v>
       </c>
       <c r="D126" t="s">
-        <v>34</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>96</v>
+        <v>32</v>
+      </c>
+      <c r="E126" t="s">
+        <v>187</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C127" s="1">
         <v>45751</v>
       </c>
       <c r="D127" t="s">
-        <v>36</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
+      </c>
+      <c r="E127" t="s">
+        <v>187</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C128" s="1">
         <v>45752</v>
       </c>
       <c r="D128" t="s">
-        <v>36</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
+      </c>
+      <c r="E128" t="s">
+        <v>187</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C129" s="1">
         <v>45753</v>
       </c>
       <c r="D129" t="s">
-        <v>36</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
+      </c>
+      <c r="E129" t="s">
+        <v>187</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C130" s="1">
         <v>45772</v>
       </c>
       <c r="D130" t="s">
-        <v>47</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
+      </c>
+      <c r="E130" t="s">
+        <v>21</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C131" s="1">
         <v>45773</v>
       </c>
       <c r="D131" t="s">
-        <v>47</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
+      </c>
+      <c r="E131" t="s">
+        <v>21</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C132" s="1">
         <v>45774</v>
       </c>
       <c r="D132" t="s">
-        <v>47</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
+      </c>
+      <c r="E132" t="s">
+        <v>21</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C133" s="1">
         <v>45787</v>
       </c>
       <c r="D133" t="s">
-        <v>33</v>
-      </c>
-      <c r="E133" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E133" t="s">
+        <v>187</v>
+      </c>
+      <c r="F133" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C134" s="1">
         <v>45788</v>
       </c>
       <c r="D134" t="s">
-        <v>33</v>
-      </c>
-      <c r="E134" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E134" t="s">
+        <v>187</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C135" s="1">
         <v>45800</v>
       </c>
       <c r="D135" t="s">
-        <v>34</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E135" t="s">
+        <v>21</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C136" s="1">
         <v>45801</v>
       </c>
       <c r="D136" t="s">
-        <v>34</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E136" t="s">
+        <v>21</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C137" s="1">
         <v>45802</v>
       </c>
       <c r="D137" t="s">
-        <v>34</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E137" t="s">
+        <v>21</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C138" s="1">
         <v>45815</v>
       </c>
       <c r="D138" t="s">
-        <v>47</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="E138" t="s">
+        <v>187</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C139" s="1">
         <v>45816</v>
       </c>
       <c r="D139" t="s">
-        <v>47</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="E139" t="s">
+        <v>187</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C140" s="1">
         <v>45829</v>
       </c>
       <c r="D140" t="s">
-        <v>47</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="E140" t="s">
+        <v>187</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C141" s="1">
         <v>45830</v>
       </c>
       <c r="D141" t="s">
-        <v>47</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="E141" t="s">
+        <v>187</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C142" s="1">
         <v>45842</v>
       </c>
       <c r="D142" t="s">
-        <v>47</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="E142" t="s">
+        <v>187</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C143" s="1">
         <v>45843</v>
       </c>
       <c r="D143" t="s">
-        <v>47</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="E143" t="s">
+        <v>187</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C144" s="1">
         <v>45844</v>
       </c>
       <c r="D144" t="s">
-        <v>47</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="E144" t="s">
+        <v>187</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C145" s="1">
         <v>45864</v>
       </c>
       <c r="D145" t="s">
-        <v>36</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
+      </c>
+      <c r="E145" t="s">
+        <v>187</v>
       </c>
       <c r="F145" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C146" s="1">
         <v>45865</v>
       </c>
       <c r="D146" t="s">
-        <v>36</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
+      </c>
+      <c r="E146" t="s">
+        <v>187</v>
       </c>
       <c r="F146" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C147" s="1">
         <v>45885</v>
       </c>
       <c r="D147" t="s">
-        <v>33</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>96</v>
+        <v>31</v>
+      </c>
+      <c r="E147" t="s">
+        <v>187</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C148" s="1">
         <v>45886</v>
       </c>
       <c r="D148" t="s">
-        <v>33</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>96</v>
+        <v>31</v>
+      </c>
+      <c r="E148" t="s">
+        <v>187</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C149" s="1">
         <v>45895</v>
       </c>
       <c r="D149" t="s">
-        <v>47</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="E149" t="s">
+        <v>187</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C150" s="1">
         <v>45896</v>
       </c>
       <c r="D150" t="s">
-        <v>47</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="E150" t="s">
+        <v>187</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C151" s="1">
         <v>45898</v>
       </c>
       <c r="D151" t="s">
-        <v>31</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="E151" t="s">
+        <v>21</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>102</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C152" s="1">
         <v>45899</v>
       </c>
       <c r="D152" t="s">
-        <v>31</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="E152" t="s">
+        <v>21</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>102</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C153" s="1">
         <v>45900</v>
       </c>
       <c r="D153" t="s">
-        <v>31</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="E153" t="s">
+        <v>21</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>102</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C154" s="1">
         <v>45905</v>
       </c>
       <c r="D154" t="s">
-        <v>34</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E154" t="s">
+        <v>21</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C155" s="1">
         <v>45906</v>
       </c>
       <c r="D155" t="s">
-        <v>34</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E155" t="s">
+        <v>21</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C156" s="1">
         <v>45907</v>
       </c>
       <c r="D156" t="s">
-        <v>34</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E156" t="s">
+        <v>21</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C157" s="1">
         <v>45927</v>
       </c>
       <c r="D157" t="s">
-        <v>36</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
+      </c>
+      <c r="E157" t="s">
+        <v>187</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C158" s="1">
         <v>45928</v>
       </c>
       <c r="D158" t="s">
-        <v>36</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
+      </c>
+      <c r="E158" t="s">
+        <v>187</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C159" s="1">
         <v>46115</v>
       </c>
       <c r="D159" t="s">
-        <v>34</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>96</v>
+        <v>32</v>
+      </c>
+      <c r="E159" t="s">
+        <v>187</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B160" s="1"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" t="s">
+        <v>36</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C160" s="1">
         <v>46116</v>
       </c>
       <c r="D160" t="s">
-        <v>34</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>96</v>
+        <v>32</v>
+      </c>
+      <c r="E160" t="s">
+        <v>187</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B161" s="1"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A161" t="s">
+        <v>36</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C161" s="1">
         <v>46117</v>
       </c>
       <c r="D161" t="s">
-        <v>34</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>96</v>
+        <v>32</v>
+      </c>
+      <c r="E161" t="s">
+        <v>187</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B162" s="1"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A162" t="s">
+        <v>36</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C162" s="1">
         <v>46118</v>
       </c>
       <c r="D162" t="s">
-        <v>33</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>96</v>
+        <v>31</v>
+      </c>
+      <c r="E162" t="s">
+        <v>187</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B163" s="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A163" t="s">
+        <v>36</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C163" s="1">
         <v>46119</v>
       </c>
       <c r="D163" t="s">
-        <v>33</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>96</v>
+        <v>31</v>
+      </c>
+      <c r="E163" t="s">
+        <v>187</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B164" s="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" t="s">
+        <v>36</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C164" s="1">
         <v>46129</v>
       </c>
       <c r="D164" t="s">
-        <v>31</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>96</v>
+        <v>29</v>
+      </c>
+      <c r="E164" t="s">
+        <v>187</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B165" s="1"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A165" t="s">
+        <v>36</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C165" s="1">
         <v>46130</v>
       </c>
       <c r="D165" t="s">
-        <v>31</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>96</v>
+        <v>29</v>
+      </c>
+      <c r="E165" t="s">
+        <v>187</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B166" s="1"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A166" t="s">
+        <v>36</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C166" s="1">
         <v>46131</v>
       </c>
       <c r="D166" t="s">
-        <v>31</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>96</v>
+        <v>29</v>
+      </c>
+      <c r="E166" t="s">
+        <v>187</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B167" s="1"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A167" t="s">
+        <v>36</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C167" s="1">
         <v>46144</v>
       </c>
       <c r="D167" t="s">
-        <v>36</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
+      </c>
+      <c r="E167" t="s">
+        <v>187</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B168" s="1"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A168" t="s">
+        <v>36</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C168" s="1">
         <v>46145</v>
       </c>
       <c r="D168" t="s">
-        <v>36</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
+      </c>
+      <c r="E168" t="s">
+        <v>187</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B169" s="1"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A169" t="s">
+        <v>36</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C169" s="1">
         <v>46147</v>
       </c>
       <c r="D169" t="s">
-        <v>31</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="E169" t="s">
+        <v>21</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B170" s="1"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A170" t="s">
+        <v>36</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C170" s="1">
         <v>46148</v>
       </c>
       <c r="D170" t="s">
-        <v>31</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="E170" t="s">
+        <v>21</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B171" s="1"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A171" t="s">
+        <v>36</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C171" s="1">
         <v>46157</v>
       </c>
       <c r="D171" t="s">
-        <v>33</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>116</v>
+        <v>31</v>
+      </c>
+      <c r="E171" t="s">
+        <v>187</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B172" s="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A172" t="s">
+        <v>36</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C172" s="1">
         <v>46158</v>
       </c>
       <c r="D172" t="s">
-        <v>33</v>
-      </c>
-      <c r="E172" s="2" t="s">
-        <v>116</v>
+        <v>31</v>
+      </c>
+      <c r="E172" t="s">
+        <v>187</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B173" s="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A173" t="s">
+        <v>36</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C173" s="1">
         <v>46159</v>
       </c>
       <c r="D173" t="s">
-        <v>33</v>
-      </c>
-      <c r="E173" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E173" t="s">
+        <v>187</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A174" t="s">
+        <v>36</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C174" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D174" t="s">
+        <v>34</v>
+      </c>
+      <c r="E174" t="s">
+        <v>21</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A175" t="s">
+        <v>36</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C175" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D175" t="s">
+        <v>34</v>
+      </c>
+      <c r="E175" t="s">
+        <v>21</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A176" t="s">
+        <v>36</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C176" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D176" t="s">
+        <v>45</v>
+      </c>
+      <c r="E176" t="s">
+        <v>187</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H176" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="H173" s="3" t="s">
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A177" t="s">
+        <v>36</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C177" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D177" t="s">
+        <v>45</v>
+      </c>
+      <c r="E177" t="s">
+        <v>187</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A178" t="s">
+        <v>36</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C178" s="1">
+        <v>46185</v>
+      </c>
+      <c r="D178" t="s">
+        <v>34</v>
+      </c>
+      <c r="E178" t="s">
+        <v>187</v>
+      </c>
+      <c r="F178" s="2" t="s">
         <v>117</v>
       </c>
+      <c r="H178" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A179" t="s">
+        <v>36</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C179" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D179" t="s">
+        <v>45</v>
+      </c>
+      <c r="E179" t="s">
+        <v>187</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A180" t="s">
+        <v>36</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C180" s="1">
+        <v>46187</v>
+      </c>
+      <c r="D180" t="s">
+        <v>45</v>
+      </c>
+      <c r="E180" t="s">
+        <v>187</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A181" t="s">
+        <v>36</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C181" s="1">
+        <v>46207</v>
+      </c>
+      <c r="D181" t="s">
+        <v>34</v>
+      </c>
+      <c r="E181" t="s">
+        <v>187</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A182" t="s">
+        <v>36</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C182" s="1">
+        <v>46208</v>
+      </c>
+      <c r="D182" t="s">
+        <v>34</v>
+      </c>
+      <c r="E182" t="s">
+        <v>187</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A183" t="s">
+        <v>36</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C183" s="1">
+        <v>46224</v>
+      </c>
+      <c r="D183" t="s">
+        <v>31</v>
+      </c>
+      <c r="E183" t="s">
+        <v>21</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A184" t="s">
+        <v>36</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C184" s="1">
+        <v>46225</v>
+      </c>
+      <c r="D184" t="s">
+        <v>31</v>
+      </c>
+      <c r="E184" t="s">
+        <v>21</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A185" t="s">
+        <v>36</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C185" s="1">
+        <v>46234</v>
+      </c>
+      <c r="D185" t="s">
+        <v>29</v>
+      </c>
+      <c r="E185" t="s">
+        <v>21</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A186" t="s">
+        <v>36</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C186" s="1">
+        <v>46235</v>
+      </c>
+      <c r="D186" t="s">
+        <v>29</v>
+      </c>
+      <c r="E186" t="s">
+        <v>21</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A187" t="s">
+        <v>36</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C187" s="1">
+        <v>46236</v>
+      </c>
+      <c r="D187" t="s">
+        <v>29</v>
+      </c>
+      <c r="E187" t="s">
+        <v>21</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A188" t="s">
+        <v>36</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C188" s="1">
+        <v>46239</v>
+      </c>
+      <c r="D188" t="s">
+        <v>45</v>
+      </c>
+      <c r="E188" t="s">
+        <v>187</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A189" t="s">
+        <v>36</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C189" s="1">
+        <v>46248</v>
+      </c>
+      <c r="D189" t="s">
+        <v>31</v>
+      </c>
+      <c r="E189" t="s">
+        <v>21</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H189" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A190" t="s">
+        <v>36</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C190" s="1">
+        <v>46249</v>
+      </c>
+      <c r="D190" t="s">
+        <v>31</v>
+      </c>
+      <c r="E190" t="s">
+        <v>21</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H190" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A191" t="s">
+        <v>36</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C191" s="1">
+        <v>46250</v>
+      </c>
+      <c r="D191" t="s">
+        <v>31</v>
+      </c>
+      <c r="E191" t="s">
+        <v>21</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H191" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A192" t="s">
+        <v>36</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C192" s="1">
+        <v>46253</v>
+      </c>
+      <c r="D192" t="s">
+        <v>29</v>
+      </c>
+      <c r="E192" t="s">
+        <v>21</v>
+      </c>
+      <c r="F192" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A193" t="s">
+        <v>36</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C193" s="1">
+        <v>46254</v>
+      </c>
+      <c r="D193" t="s">
+        <v>29</v>
+      </c>
+      <c r="E193" t="s">
+        <v>21</v>
+      </c>
+      <c r="F193" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A194" t="s">
+        <v>36</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C194" s="1">
+        <v>46262</v>
+      </c>
+      <c r="D194" t="s">
+        <v>32</v>
+      </c>
+      <c r="E194" t="s">
+        <v>187</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A195" t="s">
+        <v>36</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C195" s="1">
+        <v>46263</v>
+      </c>
+      <c r="D195" t="s">
+        <v>32</v>
+      </c>
+      <c r="E195" t="s">
+        <v>187</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A196" t="s">
+        <v>36</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C196" s="1">
+        <v>46264</v>
+      </c>
+      <c r="D196" t="s">
+        <v>32</v>
+      </c>
+      <c r="E196" t="s">
+        <v>187</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A197" t="s">
+        <v>36</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C197" s="1">
+        <v>46273</v>
+      </c>
+      <c r="D197" t="s">
+        <v>34</v>
+      </c>
+      <c r="E197" t="s">
+        <v>21</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A198" t="s">
+        <v>36</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C198" s="1">
+        <v>46274</v>
+      </c>
+      <c r="D198" t="s">
+        <v>34</v>
+      </c>
+      <c r="E198" t="s">
+        <v>21</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A199" t="s">
+        <v>36</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C199" s="1">
+        <v>46276</v>
+      </c>
+      <c r="D199" t="s">
+        <v>45</v>
+      </c>
+      <c r="E199" t="s">
+        <v>187</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A200" t="s">
+        <v>36</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C200" s="1">
+        <v>46277</v>
+      </c>
+      <c r="D200" t="s">
+        <v>45</v>
+      </c>
+      <c r="E200" t="s">
+        <v>187</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A201" t="s">
+        <v>36</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C201" s="1">
+        <v>46278</v>
+      </c>
+      <c r="D201" t="s">
+        <v>45</v>
+      </c>
+      <c r="E201" t="s">
+        <v>187</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A202" t="s">
+        <v>36</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C202" s="1">
+        <v>46291</v>
+      </c>
+      <c r="D202" t="s">
+        <v>31</v>
+      </c>
+      <c r="E202" t="s">
+        <v>187</v>
+      </c>
+      <c r="F202" t="s">
+        <v>129</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A203" t="s">
+        <v>36</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C203" s="1">
+        <v>46292</v>
+      </c>
+      <c r="D203" t="s">
+        <v>31</v>
+      </c>
+      <c r="E203" t="s">
+        <v>187</v>
+      </c>
+      <c r="F203" t="s">
+        <v>129</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A204" t="s">
+        <v>34</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C204" s="1">
+        <v>45385</v>
+      </c>
+      <c r="D204" t="s">
+        <v>45</v>
+      </c>
+      <c r="E204" t="s">
+        <v>189</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A205" t="s">
+        <v>34</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C205" s="1">
+        <v>45386</v>
+      </c>
+      <c r="D205" t="s">
+        <v>45</v>
+      </c>
+      <c r="E205" t="s">
+        <v>189</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A206" t="s">
+        <v>34</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C206" s="1">
+        <v>45395</v>
+      </c>
+      <c r="D206" t="s">
+        <v>31</v>
+      </c>
+      <c r="E206" t="s">
+        <v>189</v>
+      </c>
+      <c r="F206" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A207" t="s">
+        <v>34</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C207" s="1">
+        <v>45396</v>
+      </c>
+      <c r="D207" t="s">
+        <v>31</v>
+      </c>
+      <c r="E207" t="s">
+        <v>189</v>
+      </c>
+      <c r="F207" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A208" t="s">
+        <v>34</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C208" s="1">
+        <v>45409</v>
+      </c>
+      <c r="D208" t="s">
+        <v>36</v>
+      </c>
+      <c r="E208" t="s">
+        <v>189</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A209" t="s">
+        <v>34</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C209" s="1">
+        <v>45410</v>
+      </c>
+      <c r="D209" t="s">
+        <v>36</v>
+      </c>
+      <c r="E209" t="s">
+        <v>189</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A210" t="s">
+        <v>34</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C210" s="1">
+        <v>45423</v>
+      </c>
+      <c r="D210" t="s">
+        <v>29</v>
+      </c>
+      <c r="E210" t="s">
+        <v>189</v>
+      </c>
+      <c r="F210" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A211" t="s">
+        <v>34</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C211" s="1">
+        <v>45424</v>
+      </c>
+      <c r="D211" t="s">
+        <v>29</v>
+      </c>
+      <c r="E211" t="s">
+        <v>189</v>
+      </c>
+      <c r="F211" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A212" t="s">
+        <v>34</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C212" s="1">
+        <v>45437</v>
+      </c>
+      <c r="D212" t="s">
+        <v>32</v>
+      </c>
+      <c r="E212" t="s">
+        <v>21</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A213" t="s">
+        <v>34</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C213" s="1">
+        <v>45438</v>
+      </c>
+      <c r="D213" t="s">
+        <v>32</v>
+      </c>
+      <c r="E213" t="s">
+        <v>21</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A214" t="s">
+        <v>34</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C214" s="1">
+        <v>45444</v>
+      </c>
+      <c r="D214" t="s">
+        <v>45</v>
+      </c>
+      <c r="E214" t="s">
+        <v>189</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A215" t="s">
+        <v>34</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C215" s="1">
+        <v>45445</v>
+      </c>
+      <c r="D215" t="s">
+        <v>45</v>
+      </c>
+      <c r="E215" t="s">
+        <v>189</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A216" t="s">
+        <v>34</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C216" s="1">
+        <v>45453</v>
+      </c>
+      <c r="D216" t="s">
+        <v>31</v>
+      </c>
+      <c r="E216" t="s">
+        <v>189</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A217" t="s">
+        <v>34</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C217" s="1">
+        <v>45457</v>
+      </c>
+      <c r="D217" t="s">
+        <v>32</v>
+      </c>
+      <c r="E217" t="s">
+        <v>189</v>
+      </c>
+      <c r="F217" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A218" t="s">
+        <v>34</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C218" s="1">
+        <v>45458</v>
+      </c>
+      <c r="D218" t="s">
+        <v>32</v>
+      </c>
+      <c r="E218" t="s">
+        <v>189</v>
+      </c>
+      <c r="F218" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A219" t="s">
+        <v>34</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C219" s="1">
+        <v>45486</v>
+      </c>
+      <c r="D219" t="s">
+        <v>45</v>
+      </c>
+      <c r="E219" t="s">
+        <v>189</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A220" t="s">
+        <v>34</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C220" s="1">
+        <v>45487</v>
+      </c>
+      <c r="D220" t="s">
+        <v>45</v>
+      </c>
+      <c r="E220" t="s">
+        <v>189</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A221" t="s">
+        <v>34</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C221" s="1">
+        <v>45500</v>
+      </c>
+      <c r="D221" t="s">
+        <v>32</v>
+      </c>
+      <c r="E221" t="s">
+        <v>21</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A222" t="s">
+        <v>34</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C222" s="1">
+        <v>45501</v>
+      </c>
+      <c r="D222" t="s">
+        <v>32</v>
+      </c>
+      <c r="E222" t="s">
+        <v>21</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A223" t="s">
+        <v>34</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C223" s="1">
+        <v>45514</v>
+      </c>
+      <c r="D223" t="s">
+        <v>36</v>
+      </c>
+      <c r="E223" t="s">
+        <v>189</v>
+      </c>
+      <c r="F223" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A224" t="s">
+        <v>34</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C224" s="1">
+        <v>45515</v>
+      </c>
+      <c r="D224" t="s">
+        <v>36</v>
+      </c>
+      <c r="E224" t="s">
+        <v>189</v>
+      </c>
+      <c r="F224" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A225" t="s">
+        <v>34</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C225" s="1">
+        <v>45535</v>
+      </c>
+      <c r="D225" t="s">
+        <v>29</v>
+      </c>
+      <c r="E225" t="s">
+        <v>189</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A226" t="s">
+        <v>34</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C226" s="1">
+        <v>45536</v>
+      </c>
+      <c r="D226" t="s">
+        <v>29</v>
+      </c>
+      <c r="E226" t="s">
+        <v>189</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A227" t="s">
+        <v>34</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C227" s="1">
+        <v>45549</v>
+      </c>
+      <c r="D227" t="s">
+        <v>31</v>
+      </c>
+      <c r="E227" t="s">
+        <v>189</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A228" t="s">
+        <v>34</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C228" s="1">
+        <v>45550</v>
+      </c>
+      <c r="D228" t="s">
+        <v>31</v>
+      </c>
+      <c r="E228" t="s">
+        <v>189</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A229" t="s">
+        <v>34</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C229" s="1">
+        <v>45556</v>
+      </c>
+      <c r="D229" t="s">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>189</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A230" t="s">
+        <v>34</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C230" s="1">
+        <v>45557</v>
+      </c>
+      <c r="D230" t="s">
+        <v>36</v>
+      </c>
+      <c r="E230" t="s">
+        <v>189</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A231" t="s">
+        <v>34</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C231" s="1">
+        <v>45749</v>
+      </c>
+      <c r="D231" t="s">
+        <v>29</v>
+      </c>
+      <c r="E231" t="s">
+        <v>189</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A232" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C232" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D232" t="s">
+        <v>29</v>
+      </c>
+      <c r="E232" t="s">
+        <v>189</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A233" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C233" s="1">
+        <v>45759</v>
+      </c>
+      <c r="D233" t="s">
+        <v>32</v>
+      </c>
+      <c r="E233" t="s">
+        <v>189</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A234" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C234" s="1">
+        <v>45760</v>
+      </c>
+      <c r="D234" t="s">
+        <v>32</v>
+      </c>
+      <c r="E234" t="s">
+        <v>189</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A235" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C235" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D235" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E235" t="s">
+        <v>189</v>
+      </c>
+      <c r="F235" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G235" s="9"/>
+      <c r="H235" s="9"/>
+      <c r="I235" s="9"/>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A236" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C236" s="1">
+        <v>45774</v>
+      </c>
+      <c r="D236" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E236" t="s">
+        <v>189</v>
+      </c>
+      <c r="F236" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A237" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C237" s="1">
+        <v>45780</v>
+      </c>
+      <c r="D237" t="s">
+        <v>36</v>
+      </c>
+      <c r="E237" t="s">
+        <v>189</v>
+      </c>
+      <c r="F237" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A238" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C238" s="1">
+        <v>45781</v>
+      </c>
+      <c r="D238" t="s">
+        <v>36</v>
+      </c>
+      <c r="E238" t="s">
+        <v>189</v>
+      </c>
+      <c r="F238" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A239" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C239" s="1">
+        <v>45794</v>
+      </c>
+      <c r="D239" t="s">
+        <v>36</v>
+      </c>
+      <c r="E239" t="s">
+        <v>189</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A240" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C240" s="1">
+        <v>45795</v>
+      </c>
+      <c r="D240" t="s">
+        <v>36</v>
+      </c>
+      <c r="E240" t="s">
+        <v>189</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A241" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C241" s="1">
+        <v>45809</v>
+      </c>
+      <c r="D241" t="s">
+        <v>29</v>
+      </c>
+      <c r="E241" t="s">
+        <v>189</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A242" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C242" s="1">
+        <v>45810</v>
+      </c>
+      <c r="D242" t="s">
+        <v>29</v>
+      </c>
+      <c r="E242" t="s">
+        <v>189</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A243" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C243" s="1">
+        <v>45822</v>
+      </c>
+      <c r="D243" t="s">
+        <v>31</v>
+      </c>
+      <c r="E243" t="s">
+        <v>21</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A244" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C244" s="1">
+        <v>45823</v>
+      </c>
+      <c r="D244" t="s">
+        <v>31</v>
+      </c>
+      <c r="E244" t="s">
+        <v>21</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A245" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C245" s="1">
+        <v>45850</v>
+      </c>
+      <c r="D245" t="s">
+        <v>32</v>
+      </c>
+      <c r="E245" t="s">
+        <v>189</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A246" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C246" s="1">
+        <v>45851</v>
+      </c>
+      <c r="D246" t="s">
+        <v>32</v>
+      </c>
+      <c r="E246" t="s">
+        <v>189</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A247" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C247" s="1">
+        <v>45867</v>
+      </c>
+      <c r="D247" t="s">
+        <v>31</v>
+      </c>
+      <c r="E247" t="s">
+        <v>21</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A248" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C248" s="1">
+        <v>45868</v>
+      </c>
+      <c r="D248" t="s">
+        <v>31</v>
+      </c>
+      <c r="E248" t="s">
+        <v>21</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A249" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C249" s="1">
+        <v>45871</v>
+      </c>
+      <c r="D249" t="s">
+        <v>45</v>
+      </c>
+      <c r="E249" t="s">
+        <v>189</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A250" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C250" s="1">
+        <v>45872</v>
+      </c>
+      <c r="D250" t="s">
+        <v>45</v>
+      </c>
+      <c r="E250" t="s">
+        <v>189</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A251" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C251" s="1">
+        <v>45885</v>
+      </c>
+      <c r="D251" t="s">
+        <v>29</v>
+      </c>
+      <c r="E251" t="s">
+        <v>189</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A252" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C252" s="1">
+        <v>45886</v>
+      </c>
+      <c r="D252" t="s">
+        <v>29</v>
+      </c>
+      <c r="E252" t="s">
+        <v>189</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A253" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C253" s="1">
+        <v>45892</v>
+      </c>
+      <c r="D253" t="s">
+        <v>36</v>
+      </c>
+      <c r="E253" t="s">
+        <v>189</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A254" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C254" s="1">
+        <v>45893</v>
+      </c>
+      <c r="D254" t="s">
+        <v>36</v>
+      </c>
+      <c r="E254" t="s">
+        <v>189</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A255" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C255" s="1">
+        <v>45906</v>
+      </c>
+      <c r="D255" t="s">
+        <v>31</v>
+      </c>
+      <c r="E255" t="s">
+        <v>189</v>
+      </c>
+      <c r="F255" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A256" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C256" s="1">
+        <v>45907</v>
+      </c>
+      <c r="D256" t="s">
+        <v>31</v>
+      </c>
+      <c r="E256" t="s">
+        <v>189</v>
+      </c>
+      <c r="F256" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A257" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C257" s="1">
+        <v>45920</v>
+      </c>
+      <c r="D257" t="s">
+        <v>32</v>
+      </c>
+      <c r="E257" t="s">
+        <v>21</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A258" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C258" s="1">
+        <v>45921</v>
+      </c>
+      <c r="D258" t="s">
+        <v>32</v>
+      </c>
+      <c r="E258" t="s">
+        <v>21</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A259" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C259" s="1">
+        <v>46115</v>
+      </c>
+      <c r="D259" t="s">
+        <v>31</v>
+      </c>
+      <c r="E259" t="s">
+        <v>189</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A260" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C260" s="1">
+        <v>46116</v>
+      </c>
+      <c r="D260" t="s">
+        <v>31</v>
+      </c>
+      <c r="E260" t="s">
+        <v>189</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A261" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C261" s="1">
+        <v>46117</v>
+      </c>
+      <c r="D261" t="s">
+        <v>31</v>
+      </c>
+      <c r="E261" t="s">
+        <v>189</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A262" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C262" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D262" t="s">
+        <v>29</v>
+      </c>
+      <c r="E262" t="s">
+        <v>189</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A263" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C263" s="1">
+        <v>45400</v>
+      </c>
+      <c r="D263" t="s">
+        <v>45</v>
+      </c>
+      <c r="E263" t="s">
+        <v>189</v>
+      </c>
+      <c r="F263" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A264" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C264" s="1">
+        <v>45401</v>
+      </c>
+      <c r="D264" t="s">
+        <v>45</v>
+      </c>
+      <c r="E264" t="s">
+        <v>189</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A265" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C265" s="1">
+        <v>46151</v>
+      </c>
+      <c r="D265" t="s">
+        <v>36</v>
+      </c>
+      <c r="E265" t="s">
+        <v>189</v>
+      </c>
+      <c r="F265" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A266" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C266" s="1">
+        <v>46152</v>
+      </c>
+      <c r="D266" t="s">
+        <v>36</v>
+      </c>
+      <c r="E266" t="s">
+        <v>189</v>
+      </c>
+      <c r="F266" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A267" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C267" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D267" t="s">
+        <v>32</v>
+      </c>
+      <c r="E267" t="s">
+        <v>189</v>
+      </c>
+      <c r="F267" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A268" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C268" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D268" t="s">
+        <v>32</v>
+      </c>
+      <c r="E268" t="s">
+        <v>189</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A269" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C269" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D269" t="s">
+        <v>29</v>
+      </c>
+      <c r="E269" t="s">
+        <v>21</v>
+      </c>
+      <c r="F269" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A270" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C270" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D270" t="s">
+        <v>29</v>
+      </c>
+      <c r="E270" t="s">
+        <v>21</v>
+      </c>
+      <c r="F270" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A271" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C271" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D271" t="s">
+        <v>32</v>
+      </c>
+      <c r="E271" t="s">
+        <v>189</v>
+      </c>
+      <c r="F271" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A272" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C272" s="1">
+        <v>46187</v>
+      </c>
+      <c r="D272" t="s">
+        <v>32</v>
+      </c>
+      <c r="E272" t="s">
+        <v>189</v>
+      </c>
+      <c r="F272" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A273" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C273" s="1">
+        <v>46214</v>
+      </c>
+      <c r="D273" t="s">
+        <v>29</v>
+      </c>
+      <c r="E273" t="s">
+        <v>189</v>
+      </c>
+      <c r="F273" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A274" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C274" s="1">
+        <v>46215</v>
+      </c>
+      <c r="D274" t="s">
+        <v>29</v>
+      </c>
+      <c r="E274" t="s">
+        <v>189</v>
+      </c>
+      <c r="F274" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A275" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C275" s="1">
+        <v>46231</v>
+      </c>
+      <c r="D275" t="s">
+        <v>36</v>
+      </c>
+      <c r="E275" t="s">
+        <v>21</v>
+      </c>
+      <c r="F275" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A276" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C276" s="1">
+        <v>46232</v>
+      </c>
+      <c r="D276" t="s">
+        <v>36</v>
+      </c>
+      <c r="E276" t="s">
+        <v>21</v>
+      </c>
+      <c r="F276" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A277" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C277" s="1">
+        <v>46235</v>
+      </c>
+      <c r="D277" t="s">
+        <v>32</v>
+      </c>
+      <c r="E277" t="s">
+        <v>189</v>
+      </c>
+      <c r="F277" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A278" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C278" s="1">
+        <v>46236</v>
+      </c>
+      <c r="D278" t="s">
+        <v>32</v>
+      </c>
+      <c r="E278" t="s">
+        <v>189</v>
+      </c>
+      <c r="F278" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A279" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C279" s="1">
+        <v>46242</v>
+      </c>
+      <c r="D279" t="s">
+        <v>45</v>
+      </c>
+      <c r="E279" t="s">
+        <v>189</v>
+      </c>
+      <c r="F279" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A280" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C280" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D280" t="s">
+        <v>45</v>
+      </c>
+      <c r="E280" t="s">
+        <v>189</v>
+      </c>
+      <c r="F280" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A281" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C281" s="1">
+        <v>46256</v>
+      </c>
+      <c r="D281" t="s">
+        <v>36</v>
+      </c>
+      <c r="E281" t="s">
+        <v>189</v>
+      </c>
+      <c r="F281" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H281" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A282" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C282" s="1">
+        <v>46257</v>
+      </c>
+      <c r="D282" t="s">
+        <v>36</v>
+      </c>
+      <c r="E282" t="s">
+        <v>189</v>
+      </c>
+      <c r="F282" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H282" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A283" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C283" s="1">
+        <v>46270</v>
+      </c>
+      <c r="D283" t="s">
+        <v>31</v>
+      </c>
+      <c r="E283" t="s">
+        <v>21</v>
+      </c>
+      <c r="F283" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A284" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C284" s="1">
+        <v>46271</v>
+      </c>
+      <c r="D284" t="s">
+        <v>31</v>
+      </c>
+      <c r="E284" t="s">
+        <v>21</v>
+      </c>
+      <c r="F284" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A285" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C285" s="1">
+        <v>46291</v>
+      </c>
+      <c r="D285" t="s">
+        <v>29</v>
+      </c>
+      <c r="E285" t="s">
+        <v>189</v>
+      </c>
+      <c r="F285" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A286" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C286" s="1">
+        <v>46292</v>
+      </c>
+      <c r="D286" t="s">
+        <v>29</v>
+      </c>
+      <c r="E286" t="s">
+        <v>189</v>
+      </c>
+      <c r="F286" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A287" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C287" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D287" t="s">
+        <v>36</v>
+      </c>
+      <c r="E287" t="s">
+        <v>189</v>
+      </c>
+      <c r="F287" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A288" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C288" s="1">
+        <v>45387</v>
+      </c>
+      <c r="D288" t="s">
+        <v>34</v>
+      </c>
+      <c r="E288" t="s">
+        <v>190</v>
+      </c>
+      <c r="F288" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A289" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C289" s="1">
+        <v>45388</v>
+      </c>
+      <c r="D289" t="s">
+        <v>34</v>
+      </c>
+      <c r="E289" t="s">
+        <v>190</v>
+      </c>
+      <c r="F289" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A290" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C290" s="1">
+        <v>45389</v>
+      </c>
+      <c r="D290" t="s">
+        <v>34</v>
+      </c>
+      <c r="E290" t="s">
+        <v>190</v>
+      </c>
+      <c r="F290" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A291" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C291" s="1">
+        <v>45402</v>
+      </c>
+      <c r="D291" t="s">
+        <v>29</v>
+      </c>
+      <c r="E291" t="s">
+        <v>190</v>
+      </c>
+      <c r="F291" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H291" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A292" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C292" s="1">
+        <v>45403</v>
+      </c>
+      <c r="D292" t="s">
+        <v>29</v>
+      </c>
+      <c r="E292" t="s">
+        <v>190</v>
+      </c>
+      <c r="F292" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H292" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A293" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C293" s="1">
+        <v>45423</v>
+      </c>
+      <c r="D293" t="s">
+        <v>36</v>
+      </c>
+      <c r="E293" t="s">
+        <v>190</v>
+      </c>
+      <c r="F293" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A294" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C294" s="1">
+        <v>45424</v>
+      </c>
+      <c r="D294" t="s">
+        <v>36</v>
+      </c>
+      <c r="E294" t="s">
+        <v>190</v>
+      </c>
+      <c r="F294" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A295" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C295" s="1">
+        <v>45430</v>
+      </c>
+      <c r="D295" t="s">
+        <v>45</v>
+      </c>
+      <c r="E295" t="s">
+        <v>190</v>
+      </c>
+      <c r="F295" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A296" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C296" s="1">
+        <v>45431</v>
+      </c>
+      <c r="D296" t="s">
+        <v>45</v>
+      </c>
+      <c r="E296" t="s">
+        <v>190</v>
+      </c>
+      <c r="F296" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A297" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C297" s="1">
+        <v>45444</v>
+      </c>
+      <c r="D297" t="s">
+        <v>31</v>
+      </c>
+      <c r="E297" t="s">
+        <v>190</v>
+      </c>
+      <c r="F297" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A298" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C298" s="1">
+        <v>45445</v>
+      </c>
+      <c r="D298" t="s">
+        <v>31</v>
+      </c>
+      <c r="E298" t="s">
+        <v>190</v>
+      </c>
+      <c r="F298" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A299" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C299" s="1">
+        <v>45465</v>
+      </c>
+      <c r="D299" t="s">
+        <v>29</v>
+      </c>
+      <c r="E299" t="s">
+        <v>21</v>
+      </c>
+      <c r="F299" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H299" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A300" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C300" s="1">
+        <v>45466</v>
+      </c>
+      <c r="D300" t="s">
+        <v>29</v>
+      </c>
+      <c r="E300" t="s">
+        <v>21</v>
+      </c>
+      <c r="F300" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H300" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A301" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C301" s="1">
+        <v>45486</v>
+      </c>
+      <c r="D301" t="s">
+        <v>31</v>
+      </c>
+      <c r="E301" t="s">
+        <v>190</v>
+      </c>
+      <c r="F301" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H301" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A302" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C302" s="1">
+        <v>45487</v>
+      </c>
+      <c r="D302" t="s">
+        <v>31</v>
+      </c>
+      <c r="E302" t="s">
+        <v>190</v>
+      </c>
+      <c r="F302" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H302" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A303" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C303" s="1">
+        <v>45507</v>
+      </c>
+      <c r="D303" t="s">
+        <v>45</v>
+      </c>
+      <c r="E303" t="s">
+        <v>190</v>
+      </c>
+      <c r="F303" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H303" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A304" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C304" s="1">
+        <v>45508</v>
+      </c>
+      <c r="D304" t="s">
+        <v>45</v>
+      </c>
+      <c r="E304" t="s">
+        <v>190</v>
+      </c>
+      <c r="F304" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H304" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A305" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C305" s="1">
+        <v>45514</v>
+      </c>
+      <c r="D305" t="s">
+        <v>29</v>
+      </c>
+      <c r="E305" t="s">
+        <v>21</v>
+      </c>
+      <c r="F305" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H305" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A306" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C306" s="1">
+        <v>45515</v>
+      </c>
+      <c r="D306" t="s">
+        <v>29</v>
+      </c>
+      <c r="E306" t="s">
+        <v>21</v>
+      </c>
+      <c r="F306" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H306" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A307" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C307" s="1">
+        <v>45528</v>
+      </c>
+      <c r="D307" t="s">
+        <v>36</v>
+      </c>
+      <c r="E307" t="s">
+        <v>190</v>
+      </c>
+      <c r="F307" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A308" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C308" s="1">
+        <v>45529</v>
+      </c>
+      <c r="D308" t="s">
+        <v>36</v>
+      </c>
+      <c r="E308" t="s">
+        <v>190</v>
+      </c>
+      <c r="F308" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A309" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C309" s="4">
+        <v>45542</v>
+      </c>
+      <c r="D309" t="s">
+        <v>34</v>
+      </c>
+      <c r="E309" t="s">
+        <v>190</v>
+      </c>
+      <c r="F309" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A310" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C310" s="4">
+        <v>45543</v>
+      </c>
+      <c r="D310" t="s">
+        <v>34</v>
+      </c>
+      <c r="E310" t="s">
+        <v>190</v>
+      </c>
+      <c r="F310" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A311" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C311" s="1">
+        <v>45555</v>
+      </c>
+      <c r="D311" t="s">
+        <v>34</v>
+      </c>
+      <c r="E311" t="s">
+        <v>190</v>
+      </c>
+      <c r="F311" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H311" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A312" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C312" s="1">
+        <v>45557</v>
+      </c>
+      <c r="D312" t="s">
+        <v>31</v>
+      </c>
+      <c r="E312" t="s">
+        <v>190</v>
+      </c>
+      <c r="F312" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H312" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A313" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C313" s="1">
+        <v>45751</v>
+      </c>
+      <c r="D313" t="s">
+        <v>31</v>
+      </c>
+      <c r="E313" t="s">
+        <v>190</v>
+      </c>
+      <c r="F313" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A314" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C314" s="1">
+        <v>45752</v>
+      </c>
+      <c r="D314" t="s">
+        <v>31</v>
+      </c>
+      <c r="E314" t="s">
+        <v>190</v>
+      </c>
+      <c r="F314" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A315" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C315" s="1">
+        <v>45753</v>
+      </c>
+      <c r="D315" t="s">
+        <v>31</v>
+      </c>
+      <c r="E315" t="s">
+        <v>190</v>
+      </c>
+      <c r="F315" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A316" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C316" s="1">
+        <v>45766</v>
+      </c>
+      <c r="D316" t="s">
+        <v>36</v>
+      </c>
+      <c r="E316" t="s">
+        <v>190</v>
+      </c>
+      <c r="F316" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A317" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C317" s="1">
+        <v>45767</v>
+      </c>
+      <c r="D317" t="s">
+        <v>36</v>
+      </c>
+      <c r="E317" t="s">
+        <v>190</v>
+      </c>
+      <c r="F317" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A318" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C318" s="1">
+        <v>45793</v>
+      </c>
+      <c r="D318" t="s">
+        <v>45</v>
+      </c>
+      <c r="E318" t="s">
+        <v>190</v>
+      </c>
+      <c r="F318" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A319" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C319" s="1">
+        <v>45794</v>
+      </c>
+      <c r="D319" t="s">
+        <v>45</v>
+      </c>
+      <c r="E319" t="s">
+        <v>190</v>
+      </c>
+      <c r="F319" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A320" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C320" s="1">
+        <v>45795</v>
+      </c>
+      <c r="D320" t="s">
+        <v>45</v>
+      </c>
+      <c r="E320" t="s">
+        <v>190</v>
+      </c>
+      <c r="F320" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A321" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C321" s="1">
+        <v>45807</v>
+      </c>
+      <c r="D321" t="s">
+        <v>34</v>
+      </c>
+      <c r="E321" t="s">
+        <v>190</v>
+      </c>
+      <c r="F321" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A322" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C322" s="1">
+        <v>45808</v>
+      </c>
+      <c r="D322" t="s">
+        <v>34</v>
+      </c>
+      <c r="E322" t="s">
+        <v>190</v>
+      </c>
+      <c r="F322" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A323" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C323" s="1">
+        <v>45809</v>
+      </c>
+      <c r="D323" t="s">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>190</v>
+      </c>
+      <c r="F323" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A324" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C324" s="1">
+        <v>45822</v>
+      </c>
+      <c r="D324" t="s">
+        <v>36</v>
+      </c>
+      <c r="E324" t="s">
+        <v>190</v>
+      </c>
+      <c r="F324" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A325" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C325" s="1">
+        <v>45823</v>
+      </c>
+      <c r="D325" t="s">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>190</v>
+      </c>
+      <c r="F325" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A326" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C326" s="1">
+        <v>45843</v>
+      </c>
+      <c r="D326" t="s">
+        <v>29</v>
+      </c>
+      <c r="E326" t="s">
+        <v>190</v>
+      </c>
+      <c r="F326" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A327" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C327" s="1">
+        <v>45844</v>
+      </c>
+      <c r="D327" t="s">
+        <v>29</v>
+      </c>
+      <c r="E327" t="s">
+        <v>190</v>
+      </c>
+      <c r="F327" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A328" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C328" s="1">
+        <v>45871</v>
+      </c>
+      <c r="D328" t="s">
+        <v>36</v>
+      </c>
+      <c r="E328" t="s">
+        <v>190</v>
+      </c>
+      <c r="F328" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A329" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C329" s="1">
+        <v>45872</v>
+      </c>
+      <c r="D329" t="s">
+        <v>36</v>
+      </c>
+      <c r="E329" t="s">
+        <v>190</v>
+      </c>
+      <c r="F329" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A330" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C330" s="1">
+        <v>45885</v>
+      </c>
+      <c r="D330" t="s">
+        <v>45</v>
+      </c>
+      <c r="E330" t="s">
+        <v>190</v>
+      </c>
+      <c r="F330" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H330" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A331" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C331" s="1">
+        <v>45886</v>
+      </c>
+      <c r="D331" t="s">
+        <v>45</v>
+      </c>
+      <c r="E331" t="s">
+        <v>190</v>
+      </c>
+      <c r="F331" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H331" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A332" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C332" s="1">
+        <v>45899</v>
+      </c>
+      <c r="D332" t="s">
+        <v>31</v>
+      </c>
+      <c r="E332" t="s">
+        <v>190</v>
+      </c>
+      <c r="F332" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A333" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C333" s="1">
+        <v>45900</v>
+      </c>
+      <c r="D333" t="s">
+        <v>31</v>
+      </c>
+      <c r="E333" t="s">
+        <v>190</v>
+      </c>
+      <c r="F333" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A334" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C334" s="1">
+        <v>45913</v>
+      </c>
+      <c r="D334" t="s">
+        <v>34</v>
+      </c>
+      <c r="E334" t="s">
+        <v>190</v>
+      </c>
+      <c r="F334" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A335" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C335" s="1">
+        <v>45914</v>
+      </c>
+      <c r="D335" t="s">
+        <v>34</v>
+      </c>
+      <c r="E335" t="s">
+        <v>190</v>
+      </c>
+      <c r="F335" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A336" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C336" s="1">
+        <v>45925</v>
+      </c>
+      <c r="D336" t="s">
+        <v>31</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F336" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A337" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C337" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D337" t="s">
+        <v>31</v>
+      </c>
+      <c r="E337" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F337" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A338" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C338" s="1">
+        <v>45927</v>
+      </c>
+      <c r="D338" t="s">
+        <v>45</v>
+      </c>
+      <c r="E338" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F338" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A339" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C339" s="1">
+        <v>45928</v>
+      </c>
+      <c r="D339" t="s">
+        <v>45</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F339" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A340" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C340" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D340" t="s">
+        <v>45</v>
+      </c>
+      <c r="E340" t="s">
+        <v>190</v>
+      </c>
+      <c r="F340" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A341" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C341" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D341" t="s">
+        <v>34</v>
+      </c>
+      <c r="E341" t="s">
+        <v>190</v>
+      </c>
+      <c r="F341" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A342" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C342" s="1">
+        <v>46124</v>
+      </c>
+      <c r="D342" t="s">
+        <v>34</v>
+      </c>
+      <c r="E342" t="s">
+        <v>190</v>
+      </c>
+      <c r="F342" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A343" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C343" s="1">
+        <v>46130</v>
+      </c>
+      <c r="D343" t="s">
+        <v>31</v>
+      </c>
+      <c r="E343" t="s">
+        <v>190</v>
+      </c>
+      <c r="F343" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A344" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C344" s="1">
+        <v>46131</v>
+      </c>
+      <c r="D344" t="s">
+        <v>31</v>
+      </c>
+      <c r="E344" t="s">
+        <v>190</v>
+      </c>
+      <c r="F344" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A345" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C345" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D345" t="s">
+        <v>29</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F345" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A346" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C346" s="1">
+        <v>46144</v>
+      </c>
+      <c r="D346" t="s">
+        <v>29</v>
+      </c>
+      <c r="E346" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F346" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A347" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C347" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D347" t="s">
+        <v>29</v>
+      </c>
+      <c r="E347" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F347" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A348" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C348" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D348" t="s">
+        <v>45</v>
+      </c>
+      <c r="E348" t="s">
+        <v>190</v>
+      </c>
+      <c r="F348" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A349" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C349" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D349" t="s">
+        <v>45</v>
+      </c>
+      <c r="E349" t="s">
+        <v>190</v>
+      </c>
+      <c r="F349" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A350" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C350" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D350" t="s">
+        <v>45</v>
+      </c>
+      <c r="E350" t="s">
+        <v>190</v>
+      </c>
+      <c r="F350" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A351" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C351" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D351" t="s">
+        <v>36</v>
+      </c>
+      <c r="E351" t="s">
+        <v>190</v>
+      </c>
+      <c r="F351" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A352" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C352" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D352" t="s">
+        <v>36</v>
+      </c>
+      <c r="E352" t="s">
+        <v>190</v>
+      </c>
+      <c r="F352" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A353" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C353" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D353" t="s">
+        <v>36</v>
+      </c>
+      <c r="E353" t="s">
+        <v>190</v>
+      </c>
+      <c r="F353" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A354" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C354" s="1">
+        <v>46194</v>
+      </c>
+      <c r="D354" t="s">
+        <v>36</v>
+      </c>
+      <c r="E354" t="s">
+        <v>190</v>
+      </c>
+      <c r="F354" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A355" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B355" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C355" s="8">
+        <v>46207</v>
+      </c>
+      <c r="D355" s="9"/>
+      <c r="E355" s="9"/>
+      <c r="F355" s="9"/>
+      <c r="G355" s="9"/>
+      <c r="H355" s="9"/>
+      <c r="I355" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A173" xr:uid="{AE6A38C0-572D-4047-B9F9-1FC7841EE013}">
-      <formula1>$L$2:$L$8</formula1>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D355 A3:A355" xr:uid="{AE6A38C0-572D-4047-B9F9-1FC7841EE013}">
+      <formula1>$L$3:$L$8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B173" xr:uid="{4EFB52BD-777A-49C0-AB2C-CA7A84FB8040}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B355" xr:uid="{4EFB52BD-777A-49C0-AB2C-CA7A84FB8040}">
       <formula1>$M$3:$M$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D173" xr:uid="{E06B60E4-D0A3-4733-BC22-8A777CB2F035}">
-      <formula1>$L$3:$L$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
